--- a/output/version3/test/15-10/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>550</v>
+        <v>673</v>
       </c>
       <c r="C2" t="n">
-        <v>518</v>
+        <v>579</v>
       </c>
       <c r="D2" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E2" t="n">
-        <v>677</v>
+        <v>620</v>
       </c>
       <c r="F2" t="n">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="G2" t="n">
-        <v>568</v>
+        <v>528</v>
       </c>
       <c r="H2" t="n">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="I2" t="n">
-        <v>522</v>
+        <v>635</v>
       </c>
       <c r="J2" t="n">
-        <v>608</v>
+        <v>528</v>
       </c>
       <c r="K2" t="n">
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="L2" t="n">
-        <v>586.8</v>
+        <v>606.9</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>649</v>
+        <v>607</v>
       </c>
       <c r="C3" t="n">
-        <v>579</v>
+        <v>726</v>
       </c>
       <c r="D3" t="n">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="E3" t="n">
-        <v>516</v>
+        <v>625</v>
       </c>
       <c r="F3" t="n">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="G3" t="n">
-        <v>599</v>
+        <v>525</v>
       </c>
       <c r="H3" t="n">
-        <v>558</v>
+        <v>619</v>
       </c>
       <c r="I3" t="n">
-        <v>662</v>
+        <v>598</v>
       </c>
       <c r="J3" t="n">
-        <v>567</v>
+        <v>610</v>
       </c>
       <c r="K3" t="n">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="L3" t="n">
-        <v>611.1</v>
+        <v>626.2</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="C4" t="n">
-        <v>590</v>
+        <v>698</v>
       </c>
       <c r="D4" t="n">
-        <v>664</v>
+        <v>604</v>
       </c>
       <c r="E4" t="n">
-        <v>656</v>
+        <v>619</v>
       </c>
       <c r="F4" t="n">
-        <v>633</v>
+        <v>615</v>
       </c>
       <c r="G4" t="n">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="H4" t="n">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="I4" t="n">
-        <v>757</v>
+        <v>573</v>
       </c>
       <c r="J4" t="n">
-        <v>605</v>
+        <v>581</v>
       </c>
       <c r="K4" t="n">
-        <v>575</v>
+        <v>635</v>
       </c>
       <c r="L4" t="n">
-        <v>628.7</v>
+        <v>617.7</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>540</v>
+        <v>735</v>
       </c>
       <c r="C5" t="n">
-        <v>777</v>
+        <v>665</v>
       </c>
       <c r="D5" t="n">
-        <v>684</v>
+        <v>616</v>
       </c>
       <c r="E5" t="n">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="F5" t="n">
-        <v>625</v>
+        <v>656</v>
       </c>
       <c r="G5" t="n">
+        <v>656</v>
+      </c>
+      <c r="H5" t="n">
+        <v>681</v>
+      </c>
+      <c r="I5" t="n">
+        <v>622</v>
+      </c>
+      <c r="J5" t="n">
+        <v>659</v>
+      </c>
+      <c r="K5" t="n">
         <v>660</v>
       </c>
-      <c r="H5" t="n">
-        <v>605</v>
-      </c>
-      <c r="I5" t="n">
-        <v>604</v>
-      </c>
-      <c r="J5" t="n">
-        <v>601</v>
-      </c>
-      <c r="K5" t="n">
-        <v>628</v>
-      </c>
       <c r="L5" t="n">
-        <v>640</v>
+        <v>659.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
+        <v>659</v>
+      </c>
+      <c r="C6" t="n">
+        <v>624</v>
+      </c>
+      <c r="D6" t="n">
+        <v>588</v>
+      </c>
+      <c r="E6" t="n">
         <v>596</v>
       </c>
-      <c r="C6" t="n">
-        <v>723</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
+        <v>597</v>
+      </c>
+      <c r="G6" t="n">
+        <v>617</v>
+      </c>
+      <c r="H6" t="n">
         <v>607</v>
       </c>
-      <c r="E6" t="n">
+      <c r="I6" t="n">
         <v>633</v>
       </c>
-      <c r="F6" t="n">
-        <v>666</v>
-      </c>
-      <c r="G6" t="n">
-        <v>551</v>
-      </c>
-      <c r="H6" t="n">
-        <v>627</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
+        <v>558</v>
+      </c>
+      <c r="K6" t="n">
         <v>561</v>
       </c>
-      <c r="J6" t="n">
-        <v>557</v>
-      </c>
-      <c r="K6" t="n">
-        <v>576</v>
-      </c>
       <c r="L6" t="n">
-        <v>609.7</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>589</v>
+        <v>555</v>
       </c>
       <c r="C7" t="n">
-        <v>704</v>
+        <v>527</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>530</v>
       </c>
       <c r="E7" t="n">
-        <v>525</v>
+        <v>579</v>
       </c>
       <c r="F7" t="n">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="G7" t="n">
-        <v>587</v>
+        <v>732</v>
       </c>
       <c r="H7" t="n">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="I7" t="n">
-        <v>592</v>
+        <v>548</v>
       </c>
       <c r="J7" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K7" t="n">
-        <v>599</v>
+        <v>499</v>
       </c>
       <c r="L7" t="n">
-        <v>594.6</v>
+        <v>569.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
+        <v>663</v>
+      </c>
+      <c r="C8" t="n">
+        <v>590</v>
+      </c>
+      <c r="D8" t="n">
+        <v>636</v>
+      </c>
+      <c r="E8" t="n">
+        <v>621</v>
+      </c>
+      <c r="F8" t="n">
+        <v>625</v>
+      </c>
+      <c r="G8" t="n">
+        <v>649</v>
+      </c>
+      <c r="H8" t="n">
+        <v>546</v>
+      </c>
+      <c r="I8" t="n">
         <v>616</v>
       </c>
-      <c r="C8" t="n">
-        <v>570</v>
-      </c>
-      <c r="D8" t="n">
-        <v>548</v>
-      </c>
-      <c r="E8" t="n">
-        <v>580</v>
-      </c>
-      <c r="F8" t="n">
-        <v>590</v>
-      </c>
-      <c r="G8" t="n">
-        <v>545</v>
-      </c>
-      <c r="H8" t="n">
-        <v>598</v>
-      </c>
-      <c r="I8" t="n">
-        <v>583</v>
-      </c>
       <c r="J8" t="n">
-        <v>634</v>
+        <v>501</v>
       </c>
       <c r="K8" t="n">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="L8" t="n">
-        <v>590.2</v>
+        <v>610.6</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
+        <v>623</v>
+      </c>
+      <c r="C9" t="n">
+        <v>612</v>
+      </c>
+      <c r="D9" t="n">
+        <v>643</v>
+      </c>
+      <c r="E9" t="n">
+        <v>692</v>
+      </c>
+      <c r="F9" t="n">
+        <v>539</v>
+      </c>
+      <c r="G9" t="n">
+        <v>568</v>
+      </c>
+      <c r="H9" t="n">
+        <v>612</v>
+      </c>
+      <c r="I9" t="n">
+        <v>608</v>
+      </c>
+      <c r="J9" t="n">
+        <v>594</v>
+      </c>
+      <c r="K9" t="n">
         <v>570</v>
       </c>
-      <c r="C9" t="n">
-        <v>593</v>
-      </c>
-      <c r="D9" t="n">
-        <v>630</v>
-      </c>
-      <c r="E9" t="n">
-        <v>611</v>
-      </c>
-      <c r="F9" t="n">
-        <v>610</v>
-      </c>
-      <c r="G9" t="n">
-        <v>623</v>
-      </c>
-      <c r="H9" t="n">
-        <v>593</v>
-      </c>
-      <c r="I9" t="n">
-        <v>527</v>
-      </c>
-      <c r="J9" t="n">
-        <v>707</v>
-      </c>
-      <c r="K9" t="n">
-        <v>565</v>
-      </c>
       <c r="L9" t="n">
-        <v>602.9</v>
+        <v>606.1</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
+        <v>768</v>
+      </c>
+      <c r="C10" t="n">
+        <v>711</v>
+      </c>
+      <c r="D10" t="n">
+        <v>707</v>
+      </c>
+      <c r="E10" t="n">
+        <v>670</v>
+      </c>
+      <c r="F10" t="n">
         <v>714</v>
       </c>
-      <c r="C10" t="n">
-        <v>647</v>
-      </c>
-      <c r="D10" t="n">
-        <v>853</v>
-      </c>
-      <c r="E10" t="n">
-        <v>631</v>
-      </c>
-      <c r="F10" t="n">
-        <v>683</v>
-      </c>
       <c r="G10" t="n">
-        <v>617</v>
+        <v>761</v>
       </c>
       <c r="H10" t="n">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="I10" t="n">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="J10" t="n">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K10" t="n">
-        <v>666</v>
+        <v>701</v>
       </c>
       <c r="L10" t="n">
-        <v>709</v>
+        <v>727</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
+        <v>709</v>
+      </c>
+      <c r="C11" t="n">
+        <v>752</v>
+      </c>
+      <c r="D11" t="n">
+        <v>653</v>
+      </c>
+      <c r="E11" t="n">
+        <v>602</v>
+      </c>
+      <c r="F11" t="n">
+        <v>652</v>
+      </c>
+      <c r="G11" t="n">
+        <v>621</v>
+      </c>
+      <c r="H11" t="n">
+        <v>577</v>
+      </c>
+      <c r="I11" t="n">
+        <v>538</v>
+      </c>
+      <c r="J11" t="n">
         <v>650</v>
       </c>
-      <c r="C11" t="n">
-        <v>561</v>
-      </c>
-      <c r="D11" t="n">
-        <v>582</v>
-      </c>
-      <c r="E11" t="n">
-        <v>567</v>
-      </c>
-      <c r="F11" t="n">
-        <v>534</v>
-      </c>
-      <c r="G11" t="n">
-        <v>706</v>
-      </c>
-      <c r="H11" t="n">
-        <v>575</v>
-      </c>
-      <c r="I11" t="n">
-        <v>555</v>
-      </c>
-      <c r="J11" t="n">
-        <v>752</v>
-      </c>
       <c r="K11" t="n">
-        <v>600</v>
+        <v>572</v>
       </c>
       <c r="L11" t="n">
-        <v>608.2</v>
+        <v>632.6</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>697</v>
+        <v>621</v>
       </c>
       <c r="C12" t="n">
-        <v>660</v>
+        <v>604</v>
       </c>
       <c r="D12" t="n">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="E12" t="n">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="F12" t="n">
-        <v>560</v>
+        <v>623</v>
       </c>
       <c r="G12" t="n">
-        <v>577</v>
+        <v>690</v>
       </c>
       <c r="H12" t="n">
-        <v>587</v>
+        <v>696</v>
       </c>
       <c r="I12" t="n">
-        <v>727</v>
+        <v>665</v>
       </c>
       <c r="J12" t="n">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K12" t="n">
-        <v>570</v>
+        <v>658</v>
       </c>
       <c r="L12" t="n">
-        <v>618.7</v>
+        <v>639.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="C13" t="n">
-        <v>736</v>
+        <v>668</v>
       </c>
       <c r="D13" t="n">
-        <v>728</v>
+        <v>813</v>
       </c>
       <c r="E13" t="n">
-        <v>663</v>
+        <v>823</v>
       </c>
       <c r="F13" t="n">
-        <v>674</v>
+        <v>704</v>
       </c>
       <c r="G13" t="n">
-        <v>706</v>
+        <v>758</v>
       </c>
       <c r="H13" t="n">
-        <v>764</v>
+        <v>662</v>
       </c>
       <c r="I13" t="n">
-        <v>726</v>
+        <v>681</v>
       </c>
       <c r="J13" t="n">
-        <v>788</v>
+        <v>703</v>
       </c>
       <c r="K13" t="n">
-        <v>845</v>
+        <v>588</v>
       </c>
       <c r="L13" t="n">
-        <v>738.3</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>681</v>
+        <v>660</v>
       </c>
       <c r="C14" t="n">
-        <v>657</v>
+        <v>612</v>
       </c>
       <c r="D14" t="n">
-        <v>669</v>
+        <v>593</v>
       </c>
       <c r="E14" t="n">
-        <v>596</v>
+        <v>679</v>
       </c>
       <c r="F14" t="n">
-        <v>677</v>
+        <v>630</v>
       </c>
       <c r="G14" t="n">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="H14" t="n">
-        <v>610</v>
+        <v>769</v>
       </c>
       <c r="I14" t="n">
-        <v>828</v>
+        <v>692</v>
       </c>
       <c r="J14" t="n">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="K14" t="n">
-        <v>675</v>
+        <v>605</v>
       </c>
       <c r="L14" t="n">
-        <v>669.8</v>
+        <v>656.3</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>545</v>
+        <v>690</v>
       </c>
       <c r="C15" t="n">
-        <v>762</v>
+        <v>619</v>
       </c>
       <c r="D15" t="n">
-        <v>695</v>
+        <v>620</v>
       </c>
       <c r="E15" t="n">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F15" t="n">
-        <v>609</v>
+        <v>638</v>
       </c>
       <c r="G15" t="n">
-        <v>661</v>
+        <v>718</v>
       </c>
       <c r="H15" t="n">
-        <v>621</v>
+        <v>665</v>
       </c>
       <c r="I15" t="n">
-        <v>786</v>
+        <v>567</v>
       </c>
       <c r="J15" t="n">
-        <v>679</v>
+        <v>647</v>
       </c>
       <c r="K15" t="n">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="L15" t="n">
-        <v>665.4</v>
+        <v>648</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>679</v>
+        <v>609</v>
       </c>
       <c r="C16" t="n">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="D16" t="n">
-        <v>646</v>
+        <v>697</v>
       </c>
       <c r="E16" t="n">
-        <v>666</v>
+        <v>685</v>
       </c>
       <c r="F16" t="n">
-        <v>698</v>
+        <v>635</v>
       </c>
       <c r="G16" t="n">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="H16" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="I16" t="n">
-        <v>638</v>
+        <v>608</v>
       </c>
       <c r="J16" t="n">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="K16" t="n">
-        <v>583</v>
+        <v>631</v>
       </c>
       <c r="L16" t="n">
-        <v>651.1</v>
+        <v>648.7</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>642</v>
+        <v>542</v>
       </c>
       <c r="C17" t="n">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="D17" t="n">
-        <v>733</v>
+        <v>707</v>
       </c>
       <c r="E17" t="n">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F17" t="n">
-        <v>642</v>
+        <v>594</v>
       </c>
       <c r="G17" t="n">
-        <v>529</v>
+        <v>696</v>
       </c>
       <c r="H17" t="n">
-        <v>544</v>
+        <v>650</v>
       </c>
       <c r="I17" t="n">
-        <v>626</v>
+        <v>762</v>
       </c>
       <c r="J17" t="n">
-        <v>579</v>
+        <v>637</v>
       </c>
       <c r="K17" t="n">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="L17" t="n">
-        <v>609.2</v>
+        <v>646</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>636</v>
+        <v>574</v>
       </c>
       <c r="C18" t="n">
-        <v>709</v>
+        <v>676</v>
       </c>
       <c r="D18" t="n">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E18" t="n">
-        <v>608</v>
+        <v>729</v>
       </c>
       <c r="F18" t="n">
-        <v>598</v>
+        <v>672</v>
       </c>
       <c r="G18" t="n">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="H18" t="n">
-        <v>627</v>
+        <v>697</v>
       </c>
       <c r="I18" t="n">
+        <v>638</v>
+      </c>
+      <c r="J18" t="n">
+        <v>755</v>
+      </c>
+      <c r="K18" t="n">
         <v>603</v>
       </c>
-      <c r="J18" t="n">
-        <v>712</v>
-      </c>
-      <c r="K18" t="n">
-        <v>713</v>
-      </c>
       <c r="L18" t="n">
-        <v>651.7</v>
+        <v>664.9</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>596</v>
+        <v>712</v>
       </c>
       <c r="C19" t="n">
-        <v>620</v>
+        <v>693</v>
       </c>
       <c r="D19" t="n">
-        <v>722</v>
+        <v>689</v>
       </c>
       <c r="E19" t="n">
-        <v>650</v>
+        <v>759</v>
       </c>
       <c r="F19" t="n">
-        <v>711</v>
+        <v>657</v>
       </c>
       <c r="G19" t="n">
-        <v>634</v>
+        <v>690</v>
       </c>
       <c r="H19" t="n">
-        <v>633</v>
+        <v>676</v>
       </c>
       <c r="I19" t="n">
-        <v>659</v>
+        <v>599</v>
       </c>
       <c r="J19" t="n">
-        <v>703</v>
+        <v>639</v>
       </c>
       <c r="K19" t="n">
-        <v>608</v>
+        <v>667</v>
       </c>
       <c r="L19" t="n">
-        <v>653.6</v>
+        <v>678.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>652</v>
+        <v>809</v>
       </c>
       <c r="C20" t="n">
-        <v>695</v>
+        <v>759</v>
       </c>
       <c r="D20" t="n">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="E20" t="n">
-        <v>644</v>
+        <v>739</v>
       </c>
       <c r="F20" t="n">
-        <v>699</v>
+        <v>761</v>
       </c>
       <c r="G20" t="n">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="H20" t="n">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I20" t="n">
-        <v>667</v>
+        <v>743</v>
       </c>
       <c r="J20" t="n">
-        <v>689</v>
+        <v>807</v>
       </c>
       <c r="K20" t="n">
-        <v>719</v>
+        <v>825</v>
       </c>
       <c r="L20" t="n">
-        <v>700.2</v>
+        <v>765.4</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="C21" t="n">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="D21" t="n">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="E21" t="n">
-        <v>657</v>
+        <v>572</v>
       </c>
       <c r="F21" t="n">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="G21" t="n">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H21" t="n">
-        <v>693</v>
+        <v>655</v>
       </c>
       <c r="I21" t="n">
-        <v>709</v>
+        <v>659</v>
       </c>
       <c r="J21" t="n">
-        <v>751</v>
+        <v>613</v>
       </c>
       <c r="K21" t="n">
-        <v>661</v>
+        <v>601</v>
       </c>
       <c r="L21" t="n">
-        <v>678.6</v>
+        <v>647.4</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>556</v>
+        <v>589</v>
       </c>
       <c r="C22" t="n">
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="D22" t="n">
-        <v>614</v>
+        <v>647</v>
       </c>
       <c r="E22" t="n">
-        <v>605</v>
+        <v>669</v>
       </c>
       <c r="F22" t="n">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="G22" t="n">
-        <v>626</v>
+        <v>595</v>
       </c>
       <c r="H22" t="n">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="I22" t="n">
-        <v>672</v>
+        <v>557</v>
       </c>
       <c r="J22" t="n">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="K22" t="n">
-        <v>682</v>
+        <v>696</v>
       </c>
       <c r="L22" t="n">
-        <v>616</v>
+        <v>628.4</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>562</v>
+        <v>685</v>
       </c>
       <c r="C23" t="n">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="D23" t="n">
-        <v>657</v>
+        <v>592</v>
       </c>
       <c r="E23" t="n">
-        <v>777</v>
+        <v>565</v>
       </c>
       <c r="F23" t="n">
-        <v>628</v>
+        <v>586</v>
       </c>
       <c r="G23" t="n">
-        <v>635</v>
+        <v>720</v>
       </c>
       <c r="H23" t="n">
-        <v>592</v>
+        <v>678</v>
       </c>
       <c r="I23" t="n">
-        <v>600</v>
+        <v>637</v>
       </c>
       <c r="J23" t="n">
-        <v>573</v>
+        <v>630</v>
       </c>
       <c r="K23" t="n">
-        <v>575</v>
+        <v>640</v>
       </c>
       <c r="L23" t="n">
-        <v>624.6</v>
+        <v>638.9</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>724</v>
+        <v>640</v>
       </c>
       <c r="C24" t="n">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="D24" t="n">
-        <v>638</v>
+        <v>800</v>
       </c>
       <c r="E24" t="n">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="F24" t="n">
+        <v>614</v>
+      </c>
+      <c r="G24" t="n">
         <v>726</v>
       </c>
-      <c r="G24" t="n">
-        <v>621</v>
-      </c>
       <c r="H24" t="n">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="I24" t="n">
-        <v>661</v>
+        <v>576</v>
       </c>
       <c r="J24" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="K24" t="n">
-        <v>631</v>
+        <v>756</v>
       </c>
       <c r="L24" t="n">
-        <v>663.2</v>
+        <v>675.8</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>668</v>
+        <v>616</v>
       </c>
       <c r="C25" t="n">
-        <v>696</v>
+        <v>628</v>
       </c>
       <c r="D25" t="n">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E25" t="n">
-        <v>673</v>
+        <v>629</v>
       </c>
       <c r="F25" t="n">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="G25" t="n">
-        <v>684</v>
+        <v>656</v>
       </c>
       <c r="H25" t="n">
-        <v>753</v>
+        <v>594</v>
       </c>
       <c r="I25" t="n">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="J25" t="n">
-        <v>661</v>
+        <v>598</v>
       </c>
       <c r="K25" t="n">
-        <v>637</v>
+        <v>600</v>
       </c>
       <c r="L25" t="n">
-        <v>672.6</v>
+        <v>638.4</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>595</v>
+        <v>630</v>
       </c>
       <c r="C26" t="n">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="D26" t="n">
-        <v>687</v>
+        <v>621</v>
       </c>
       <c r="E26" t="n">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="F26" t="n">
-        <v>682</v>
+        <v>746</v>
       </c>
       <c r="G26" t="n">
-        <v>660</v>
+        <v>626</v>
       </c>
       <c r="H26" t="n">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="I26" t="n">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="J26" t="n">
-        <v>661</v>
+        <v>692</v>
       </c>
       <c r="K26" t="n">
-        <v>693</v>
+        <v>676</v>
       </c>
       <c r="L26" t="n">
-        <v>658.6</v>
+        <v>656.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="C27" t="n">
-        <v>554</v>
+        <v>509</v>
       </c>
       <c r="D27" t="n">
-        <v>494</v>
+        <v>534</v>
       </c>
       <c r="E27" t="n">
-        <v>527</v>
+        <v>609</v>
       </c>
       <c r="F27" t="n">
-        <v>640</v>
+        <v>582</v>
       </c>
       <c r="G27" t="n">
-        <v>512</v>
+        <v>764</v>
       </c>
       <c r="H27" t="n">
-        <v>584</v>
+        <v>636</v>
       </c>
       <c r="I27" t="n">
-        <v>522</v>
+        <v>582</v>
       </c>
       <c r="J27" t="n">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="K27" t="n">
-        <v>511</v>
+        <v>546</v>
       </c>
       <c r="L27" t="n">
-        <v>548.6</v>
+        <v>590.2</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>710</v>
+        <v>604</v>
       </c>
       <c r="C28" t="n">
-        <v>632</v>
+        <v>575</v>
       </c>
       <c r="D28" t="n">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="E28" t="n">
-        <v>718</v>
+        <v>597</v>
       </c>
       <c r="F28" t="n">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="G28" t="n">
-        <v>631</v>
+        <v>712</v>
       </c>
       <c r="H28" t="n">
-        <v>648</v>
+        <v>622</v>
       </c>
       <c r="I28" t="n">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="J28" t="n">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="K28" t="n">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="L28" t="n">
-        <v>644</v>
+        <v>621.9</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="C29" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="D29" t="n">
-        <v>722</v>
+        <v>619</v>
       </c>
       <c r="E29" t="n">
-        <v>576</v>
+        <v>724</v>
       </c>
       <c r="F29" t="n">
-        <v>580</v>
+        <v>665</v>
       </c>
       <c r="G29" t="n">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="H29" t="n">
-        <v>739</v>
+        <v>608</v>
       </c>
       <c r="I29" t="n">
-        <v>646</v>
+        <v>598</v>
       </c>
       <c r="J29" t="n">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="K29" t="n">
-        <v>645</v>
+        <v>726</v>
       </c>
       <c r="L29" t="n">
-        <v>652.2</v>
+        <v>659</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C30" t="n">
-        <v>626</v>
+        <v>679</v>
       </c>
       <c r="D30" t="n">
-        <v>699</v>
+        <v>638</v>
       </c>
       <c r="E30" t="n">
-        <v>651</v>
+        <v>594</v>
       </c>
       <c r="F30" t="n">
-        <v>595</v>
+        <v>698</v>
       </c>
       <c r="G30" t="n">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="H30" t="n">
-        <v>698</v>
+        <v>652</v>
       </c>
       <c r="I30" t="n">
-        <v>663</v>
+        <v>628</v>
       </c>
       <c r="J30" t="n">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="K30" t="n">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="L30" t="n">
-        <v>644.9</v>
+        <v>643.4</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="C31" t="n">
-        <v>747</v>
+        <v>797</v>
       </c>
       <c r="D31" t="n">
-        <v>733</v>
+        <v>691</v>
       </c>
       <c r="E31" t="n">
-        <v>736</v>
+        <v>764</v>
       </c>
       <c r="F31" t="n">
-        <v>756</v>
+        <v>702</v>
       </c>
       <c r="G31" t="n">
-        <v>690</v>
+        <v>713</v>
       </c>
       <c r="H31" t="n">
-        <v>813</v>
+        <v>726</v>
       </c>
       <c r="I31" t="n">
-        <v>696</v>
+        <v>811</v>
       </c>
       <c r="J31" t="n">
-        <v>847</v>
+        <v>692</v>
       </c>
       <c r="K31" t="n">
-        <v>706</v>
+        <v>750</v>
       </c>
       <c r="L31" t="n">
-        <v>745.1</v>
+        <v>738.3</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
+        <v>721</v>
+      </c>
+      <c r="C32" t="n">
+        <v>691</v>
+      </c>
+      <c r="D32" t="n">
+        <v>656</v>
+      </c>
+      <c r="E32" t="n">
+        <v>720</v>
+      </c>
+      <c r="F32" t="n">
+        <v>675</v>
+      </c>
+      <c r="G32" t="n">
+        <v>647</v>
+      </c>
+      <c r="H32" t="n">
+        <v>678</v>
+      </c>
+      <c r="I32" t="n">
         <v>737</v>
       </c>
-      <c r="C32" t="n">
-        <v>618</v>
-      </c>
-      <c r="D32" t="n">
-        <v>606</v>
-      </c>
-      <c r="E32" t="n">
-        <v>670</v>
-      </c>
-      <c r="F32" t="n">
-        <v>667</v>
-      </c>
-      <c r="G32" t="n">
-        <v>630</v>
-      </c>
-      <c r="H32" t="n">
-        <v>656</v>
-      </c>
-      <c r="I32" t="n">
-        <v>764</v>
-      </c>
       <c r="J32" t="n">
-        <v>685</v>
+        <v>626</v>
       </c>
       <c r="K32" t="n">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="L32" t="n">
-        <v>669.7</v>
+        <v>680.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>844</v>
+        <v>702</v>
       </c>
       <c r="C33" t="n">
-        <v>670</v>
+        <v>700</v>
       </c>
       <c r="D33" t="n">
-        <v>691</v>
+        <v>732</v>
       </c>
       <c r="E33" t="n">
-        <v>623</v>
+        <v>587</v>
       </c>
       <c r="F33" t="n">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="G33" t="n">
-        <v>744</v>
+        <v>642</v>
       </c>
       <c r="H33" t="n">
-        <v>719</v>
+        <v>702</v>
       </c>
       <c r="I33" t="n">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="J33" t="n">
-        <v>654</v>
+        <v>767</v>
       </c>
       <c r="K33" t="n">
-        <v>608</v>
+        <v>718</v>
       </c>
       <c r="L33" t="n">
-        <v>682.4</v>
+        <v>681</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>637</v>
+        <v>573</v>
       </c>
       <c r="C34" t="n">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="D34" t="n">
-        <v>656</v>
+        <v>601</v>
       </c>
       <c r="E34" t="n">
-        <v>547</v>
+        <v>595</v>
       </c>
       <c r="F34" t="n">
-        <v>628</v>
+        <v>677</v>
       </c>
       <c r="G34" t="n">
-        <v>662</v>
+        <v>744</v>
       </c>
       <c r="H34" t="n">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="I34" t="n">
-        <v>625</v>
+        <v>694</v>
       </c>
       <c r="J34" t="n">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="K34" t="n">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="L34" t="n">
-        <v>635.5</v>
+        <v>641.1</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="C35" t="n">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="D35" t="n">
-        <v>708</v>
+        <v>621</v>
       </c>
       <c r="E35" t="n">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="F35" t="n">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G35" t="n">
-        <v>570</v>
+        <v>641</v>
       </c>
       <c r="H35" t="n">
         <v>593</v>
       </c>
       <c r="I35" t="n">
-        <v>656</v>
+        <v>611</v>
       </c>
       <c r="J35" t="n">
-        <v>605</v>
+        <v>561</v>
       </c>
       <c r="K35" t="n">
-        <v>639</v>
+        <v>571</v>
       </c>
       <c r="L35" t="n">
-        <v>609.1</v>
+        <v>592.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C36" t="n">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D36" t="n">
-        <v>593</v>
+        <v>652</v>
       </c>
       <c r="E36" t="n">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="F36" t="n">
+        <v>695</v>
+      </c>
+      <c r="G36" t="n">
         <v>715</v>
       </c>
-      <c r="G36" t="n">
-        <v>577</v>
-      </c>
       <c r="H36" t="n">
-        <v>677</v>
+        <v>642</v>
       </c>
       <c r="I36" t="n">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="J36" t="n">
-        <v>724</v>
+        <v>634</v>
       </c>
       <c r="K36" t="n">
-        <v>650</v>
+        <v>609</v>
       </c>
       <c r="L36" t="n">
-        <v>664.2</v>
+        <v>665.2</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>584</v>
+        <v>755</v>
       </c>
       <c r="C37" t="n">
+        <v>733</v>
+      </c>
+      <c r="D37" t="n">
+        <v>688</v>
+      </c>
+      <c r="E37" t="n">
+        <v>729</v>
+      </c>
+      <c r="F37" t="n">
+        <v>745</v>
+      </c>
+      <c r="G37" t="n">
+        <v>667</v>
+      </c>
+      <c r="H37" t="n">
+        <v>663</v>
+      </c>
+      <c r="I37" t="n">
+        <v>639</v>
+      </c>
+      <c r="J37" t="n">
         <v>657</v>
       </c>
-      <c r="D37" t="n">
-        <v>791</v>
-      </c>
-      <c r="E37" t="n">
-        <v>688</v>
-      </c>
-      <c r="F37" t="n">
-        <v>697</v>
-      </c>
-      <c r="G37" t="n">
-        <v>570</v>
-      </c>
-      <c r="H37" t="n">
-        <v>667</v>
-      </c>
-      <c r="I37" t="n">
-        <v>702</v>
-      </c>
-      <c r="J37" t="n">
-        <v>686</v>
-      </c>
       <c r="K37" t="n">
-        <v>661</v>
+        <v>637</v>
       </c>
       <c r="L37" t="n">
-        <v>670.3</v>
+        <v>691.3</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>618</v>
+        <v>677</v>
       </c>
       <c r="C38" t="n">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="D38" t="n">
-        <v>752</v>
+        <v>597</v>
       </c>
       <c r="E38" t="n">
-        <v>683</v>
+        <v>560</v>
       </c>
       <c r="F38" t="n">
-        <v>564</v>
+        <v>604</v>
       </c>
       <c r="G38" t="n">
+        <v>628</v>
+      </c>
+      <c r="H38" t="n">
+        <v>665</v>
+      </c>
+      <c r="I38" t="n">
         <v>599</v>
       </c>
-      <c r="H38" t="n">
-        <v>667</v>
-      </c>
-      <c r="I38" t="n">
-        <v>610</v>
-      </c>
       <c r="J38" t="n">
-        <v>635</v>
+        <v>606</v>
       </c>
       <c r="K38" t="n">
-        <v>667</v>
+        <v>608</v>
       </c>
       <c r="L38" t="n">
-        <v>639.7</v>
+        <v>618.5</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>497</v>
+        <v>629</v>
       </c>
       <c r="C39" t="n">
-        <v>637</v>
+        <v>509</v>
       </c>
       <c r="D39" t="n">
-        <v>663</v>
+        <v>636</v>
       </c>
       <c r="E39" t="n">
-        <v>484</v>
+        <v>533</v>
       </c>
       <c r="F39" t="n">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="G39" t="n">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H39" t="n">
-        <v>611</v>
+        <v>536</v>
       </c>
       <c r="I39" t="n">
-        <v>538</v>
+        <v>512</v>
       </c>
       <c r="J39" t="n">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="K39" t="n">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="L39" t="n">
-        <v>571.9</v>
+        <v>559.4</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="C40" t="n">
-        <v>653</v>
+        <v>748</v>
       </c>
       <c r="D40" t="n">
-        <v>726</v>
+        <v>694</v>
       </c>
       <c r="E40" t="n">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="F40" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="G40" t="n">
-        <v>717</v>
+        <v>625</v>
       </c>
       <c r="H40" t="n">
-        <v>634</v>
+        <v>750</v>
       </c>
       <c r="I40" t="n">
-        <v>602</v>
+        <v>671</v>
       </c>
       <c r="J40" t="n">
-        <v>579</v>
+        <v>735</v>
       </c>
       <c r="K40" t="n">
-        <v>682</v>
+        <v>767</v>
       </c>
       <c r="L40" t="n">
-        <v>669.5</v>
+        <v>709.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
+        <v>668</v>
+      </c>
+      <c r="C41" t="n">
+        <v>595</v>
+      </c>
+      <c r="D41" t="n">
         <v>516</v>
       </c>
-      <c r="C41" t="n">
-        <v>583</v>
-      </c>
-      <c r="D41" t="n">
-        <v>678</v>
-      </c>
       <c r="E41" t="n">
-        <v>592</v>
+        <v>556</v>
       </c>
       <c r="F41" t="n">
-        <v>686</v>
+        <v>651</v>
       </c>
       <c r="G41" t="n">
-        <v>557</v>
+        <v>702</v>
       </c>
       <c r="H41" t="n">
-        <v>573</v>
+        <v>636</v>
       </c>
       <c r="I41" t="n">
-        <v>628</v>
+        <v>706</v>
       </c>
       <c r="J41" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K41" t="n">
-        <v>530</v>
+        <v>636</v>
       </c>
       <c r="L41" t="n">
-        <v>595.7</v>
+        <v>628.1</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>786</v>
+        <v>593</v>
       </c>
       <c r="C42" t="n">
-        <v>678</v>
+        <v>606</v>
       </c>
       <c r="D42" t="n">
-        <v>711</v>
+        <v>676</v>
       </c>
       <c r="E42" t="n">
-        <v>664</v>
+        <v>694</v>
       </c>
       <c r="F42" t="n">
-        <v>708</v>
+        <v>623</v>
       </c>
       <c r="G42" t="n">
-        <v>644</v>
+        <v>722</v>
       </c>
       <c r="H42" t="n">
-        <v>612</v>
+        <v>697</v>
       </c>
       <c r="I42" t="n">
-        <v>622</v>
+        <v>672</v>
       </c>
       <c r="J42" t="n">
-        <v>598</v>
+        <v>726</v>
       </c>
       <c r="K42" t="n">
-        <v>573</v>
+        <v>707</v>
       </c>
       <c r="L42" t="n">
-        <v>659.6</v>
+        <v>671.6</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>782</v>
+        <v>740</v>
       </c>
       <c r="C43" t="n">
-        <v>680</v>
+        <v>728</v>
       </c>
       <c r="D43" t="n">
-        <v>625</v>
+        <v>714</v>
       </c>
       <c r="E43" t="n">
-        <v>606</v>
+        <v>795</v>
       </c>
       <c r="F43" t="n">
-        <v>753</v>
+        <v>731</v>
       </c>
       <c r="G43" t="n">
-        <v>729</v>
+        <v>701</v>
       </c>
       <c r="H43" t="n">
-        <v>707</v>
+        <v>732</v>
       </c>
       <c r="I43" t="n">
-        <v>726</v>
+        <v>743</v>
       </c>
       <c r="J43" t="n">
-        <v>732</v>
+        <v>666</v>
       </c>
       <c r="K43" t="n">
-        <v>712</v>
+        <v>795</v>
       </c>
       <c r="L43" t="n">
-        <v>705.2</v>
+        <v>734.5</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="C44" t="n">
-        <v>708</v>
+        <v>625</v>
       </c>
       <c r="D44" t="n">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="E44" t="n">
-        <v>696</v>
+        <v>620</v>
       </c>
       <c r="F44" t="n">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="G44" t="n">
-        <v>730</v>
+        <v>585</v>
       </c>
       <c r="H44" t="n">
-        <v>640</v>
+        <v>582</v>
       </c>
       <c r="I44" t="n">
-        <v>616</v>
+        <v>597</v>
       </c>
       <c r="J44" t="n">
-        <v>714</v>
+        <v>621</v>
       </c>
       <c r="K44" t="n">
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="L44" t="n">
-        <v>660.9</v>
+        <v>613.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
+        <v>662</v>
+      </c>
+      <c r="C45" t="n">
+        <v>657</v>
+      </c>
+      <c r="D45" t="n">
+        <v>639</v>
+      </c>
+      <c r="E45" t="n">
+        <v>670</v>
+      </c>
+      <c r="F45" t="n">
+        <v>691</v>
+      </c>
+      <c r="G45" t="n">
+        <v>685</v>
+      </c>
+      <c r="H45" t="n">
+        <v>647</v>
+      </c>
+      <c r="I45" t="n">
+        <v>634</v>
+      </c>
+      <c r="J45" t="n">
         <v>623</v>
       </c>
-      <c r="C45" t="n">
-        <v>754</v>
-      </c>
-      <c r="D45" t="n">
-        <v>634</v>
-      </c>
-      <c r="E45" t="n">
-        <v>734</v>
-      </c>
-      <c r="F45" t="n">
-        <v>650</v>
-      </c>
-      <c r="G45" t="n">
-        <v>677</v>
-      </c>
-      <c r="H45" t="n">
-        <v>660</v>
-      </c>
-      <c r="I45" t="n">
-        <v>596</v>
-      </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
+        <v>682</v>
+      </c>
+      <c r="L45" t="n">
         <v>659</v>
-      </c>
-      <c r="K45" t="n">
-        <v>714</v>
-      </c>
-      <c r="L45" t="n">
-        <v>670.1</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C46" t="n">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="D46" t="n">
-        <v>616</v>
+        <v>702</v>
       </c>
       <c r="E46" t="n">
-        <v>663</v>
+        <v>719</v>
       </c>
       <c r="F46" t="n">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="G46" t="n">
-        <v>652</v>
+        <v>686</v>
       </c>
       <c r="H46" t="n">
         <v>655</v>
       </c>
       <c r="I46" t="n">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="J46" t="n">
-        <v>701</v>
+        <v>621</v>
       </c>
       <c r="K46" t="n">
-        <v>629</v>
+        <v>658</v>
       </c>
       <c r="L46" t="n">
-        <v>643</v>
+        <v>657.1</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>650</v>
+        <v>585</v>
       </c>
       <c r="C47" t="n">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="D47" t="n">
-        <v>590</v>
+        <v>557</v>
       </c>
       <c r="E47" t="n">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="F47" t="n">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="G47" t="n">
-        <v>719</v>
+        <v>585</v>
       </c>
       <c r="H47" t="n">
-        <v>595</v>
+        <v>770</v>
       </c>
       <c r="I47" t="n">
-        <v>662</v>
+        <v>545</v>
       </c>
       <c r="J47" t="n">
-        <v>534</v>
+        <v>620</v>
       </c>
       <c r="K47" t="n">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="L47" t="n">
-        <v>625.6</v>
+        <v>615.1</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>798</v>
+        <v>684</v>
       </c>
       <c r="C48" t="n">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="D48" t="n">
-        <v>633</v>
+        <v>710</v>
       </c>
       <c r="E48" t="n">
-        <v>701</v>
+        <v>655</v>
       </c>
       <c r="F48" t="n">
-        <v>728</v>
+        <v>678</v>
       </c>
       <c r="G48" t="n">
-        <v>800</v>
+        <v>705</v>
       </c>
       <c r="H48" t="n">
-        <v>675</v>
+        <v>694</v>
       </c>
       <c r="I48" t="n">
-        <v>681</v>
+        <v>707</v>
       </c>
       <c r="J48" t="n">
-        <v>651</v>
+        <v>687</v>
       </c>
       <c r="K48" t="n">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="L48" t="n">
-        <v>709.5</v>
+        <v>695.7</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>680</v>
+        <v>814</v>
       </c>
       <c r="C49" t="n">
+        <v>847</v>
+      </c>
+      <c r="D49" t="n">
+        <v>756</v>
+      </c>
+      <c r="E49" t="n">
+        <v>714</v>
+      </c>
+      <c r="F49" t="n">
+        <v>736</v>
+      </c>
+      <c r="G49" t="n">
+        <v>661</v>
+      </c>
+      <c r="H49" t="n">
+        <v>732</v>
+      </c>
+      <c r="I49" t="n">
+        <v>669</v>
+      </c>
+      <c r="J49" t="n">
+        <v>739</v>
+      </c>
+      <c r="K49" t="n">
         <v>718</v>
       </c>
-      <c r="D49" t="n">
-        <v>719</v>
-      </c>
-      <c r="E49" t="n">
-        <v>771</v>
-      </c>
-      <c r="F49" t="n">
-        <v>730</v>
-      </c>
-      <c r="G49" t="n">
-        <v>832</v>
-      </c>
-      <c r="H49" t="n">
-        <v>734</v>
-      </c>
-      <c r="I49" t="n">
-        <v>717</v>
-      </c>
-      <c r="J49" t="n">
-        <v>725</v>
-      </c>
-      <c r="K49" t="n">
-        <v>603</v>
-      </c>
       <c r="L49" t="n">
-        <v>722.9</v>
+        <v>738.6</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>743</v>
+        <v>620</v>
       </c>
       <c r="C50" t="n">
-        <v>618</v>
+        <v>702</v>
       </c>
       <c r="D50" t="n">
-        <v>692</v>
+        <v>582</v>
       </c>
       <c r="E50" t="n">
-        <v>660</v>
+        <v>615</v>
       </c>
       <c r="F50" t="n">
-        <v>582</v>
+        <v>707</v>
       </c>
       <c r="G50" t="n">
-        <v>587</v>
+        <v>678</v>
       </c>
       <c r="H50" t="n">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="I50" t="n">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="J50" t="n">
-        <v>604</v>
+        <v>656</v>
       </c>
       <c r="K50" t="n">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="L50" t="n">
-        <v>639.6</v>
+        <v>653.1</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>761</v>
+        <v>655</v>
       </c>
       <c r="C51" t="n">
-        <v>598</v>
+        <v>748</v>
       </c>
       <c r="D51" t="n">
-        <v>671</v>
+        <v>708</v>
       </c>
       <c r="E51" t="n">
-        <v>618</v>
+        <v>663</v>
       </c>
       <c r="F51" t="n">
-        <v>648</v>
+        <v>719</v>
       </c>
       <c r="G51" t="n">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="H51" t="n">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="I51" t="n">
-        <v>778</v>
+        <v>663</v>
       </c>
       <c r="J51" t="n">
-        <v>692</v>
+        <v>639</v>
       </c>
       <c r="K51" t="n">
-        <v>624</v>
+        <v>690</v>
       </c>
       <c r="L51" t="n">
-        <v>676.7</v>
+        <v>687.9</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>649.8200000000001</v>
+        <v>660.58</v>
       </c>
       <c r="C52" t="n">
-        <v>649.36</v>
+        <v>657.12</v>
       </c>
       <c r="D52" t="n">
-        <v>665.96</v>
+        <v>653.74</v>
       </c>
       <c r="E52" t="n">
-        <v>638.5</v>
+        <v>650.64</v>
       </c>
       <c r="F52" t="n">
-        <v>646.12</v>
+        <v>652.62</v>
       </c>
       <c r="G52" t="n">
-        <v>642.54</v>
+        <v>665.6</v>
       </c>
       <c r="H52" t="n">
-        <v>649.8</v>
+        <v>660.7</v>
       </c>
       <c r="I52" t="n">
-        <v>652.16</v>
+        <v>642</v>
       </c>
       <c r="J52" t="n">
-        <v>651.88</v>
+        <v>639.12</v>
       </c>
       <c r="K52" t="n">
-        <v>635.6</v>
+        <v>649.14</v>
       </c>
       <c r="L52" t="n">
-        <v>648.174</v>
+        <v>653.1260000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.694422483444214</v>
+        <v>4.684290885925293</v>
       </c>
       <c r="C2" t="n">
-        <v>4.275994300842285</v>
+        <v>4.351162910461426</v>
       </c>
       <c r="D2" t="n">
-        <v>5.545967578887939</v>
+        <v>4.298319101333618</v>
       </c>
       <c r="E2" t="n">
-        <v>5.703540325164795</v>
+        <v>4.288342952728271</v>
       </c>
       <c r="F2" t="n">
-        <v>4.465340614318848</v>
+        <v>4.301301956176758</v>
       </c>
       <c r="G2" t="n">
-        <v>4.611111640930176</v>
+        <v>4.535703182220459</v>
       </c>
       <c r="H2" t="n">
-        <v>4.791982412338257</v>
+        <v>4.332219362258911</v>
       </c>
       <c r="I2" t="n">
-        <v>4.402390956878662</v>
+        <v>4.145212173461914</v>
       </c>
       <c r="J2" t="n">
-        <v>4.292697906494141</v>
+        <v>4.049456834793091</v>
       </c>
       <c r="K2" t="n">
-        <v>4.241963624954224</v>
+        <v>4.209043979644775</v>
       </c>
       <c r="L2" t="n">
-        <v>4.702541184425354</v>
+        <v>4.319505333900452</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.325214147567749</v>
+        <v>4.344183444976807</v>
       </c>
       <c r="C3" t="n">
-        <v>4.171472311019897</v>
+        <v>5.293731689453125</v>
       </c>
       <c r="D3" t="n">
-        <v>5.303014278411865</v>
+        <v>5.574522495269775</v>
       </c>
       <c r="E3" t="n">
-        <v>4.273993968963623</v>
+        <v>4.381590127944946</v>
       </c>
       <c r="F3" t="n">
-        <v>4.608372449874878</v>
+        <v>4.541685104370117</v>
       </c>
       <c r="G3" t="n">
-        <v>4.261214017868042</v>
+        <v>4.452402353286743</v>
       </c>
       <c r="H3" t="n">
-        <v>4.420318841934204</v>
+        <v>4.409517288208008</v>
       </c>
       <c r="I3" t="n">
-        <v>4.866990089416504</v>
+        <v>4.514777660369873</v>
       </c>
       <c r="J3" t="n">
-        <v>4.604370832443237</v>
+        <v>4.707249164581299</v>
       </c>
       <c r="K3" t="n">
-        <v>4.574307918548584</v>
+        <v>4.444922924041748</v>
       </c>
       <c r="L3" t="n">
-        <v>4.540926885604859</v>
+        <v>4.666458225250244</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.194545030593872</v>
+        <v>4.197070598602295</v>
       </c>
       <c r="C4" t="n">
-        <v>4.081196308135986</v>
+        <v>4.034479141235352</v>
       </c>
       <c r="D4" t="n">
-        <v>3.902836084365845</v>
+        <v>3.839030265808105</v>
       </c>
       <c r="E4" t="n">
-        <v>4.069451093673706</v>
+        <v>4.021511554718018</v>
       </c>
       <c r="F4" t="n">
-        <v>4.549620866775513</v>
+        <v>3.649991750717163</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14138388633728</v>
+        <v>3.891379117965698</v>
       </c>
       <c r="H4" t="n">
-        <v>4.369079828262329</v>
+        <v>4.212057590484619</v>
       </c>
       <c r="I4" t="n">
-        <v>5.235536098480225</v>
+        <v>3.781651258468628</v>
       </c>
       <c r="J4" t="n">
-        <v>4.55109715461731</v>
+        <v>3.664974212646484</v>
       </c>
       <c r="K4" t="n">
-        <v>4.332136869430542</v>
+        <v>4.034534215927124</v>
       </c>
       <c r="L4" t="n">
-        <v>4.342688322067261</v>
+        <v>3.932667970657349</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.069857597351074</v>
+        <v>4.242454528808594</v>
       </c>
       <c r="C5" t="n">
-        <v>5.586459159851074</v>
+        <v>4.120755672454834</v>
       </c>
       <c r="D5" t="n">
-        <v>3.994843721389771</v>
+        <v>4.30429220199585</v>
       </c>
       <c r="E5" t="n">
-        <v>4.056195735931396</v>
+        <v>4.43745493888855</v>
       </c>
       <c r="F5" t="n">
-        <v>3.735973119735718</v>
+        <v>4.397552967071533</v>
       </c>
       <c r="G5" t="n">
-        <v>3.909541606903076</v>
+        <v>4.150688648223877</v>
       </c>
       <c r="H5" t="n">
-        <v>3.796322584152222</v>
+        <v>4.310279369354248</v>
       </c>
       <c r="I5" t="n">
-        <v>3.612798452377319</v>
+        <v>4.088828563690186</v>
       </c>
       <c r="J5" t="n">
-        <v>3.659680128097534</v>
+        <v>3.952714920043945</v>
       </c>
       <c r="K5" t="n">
-        <v>3.769403696060181</v>
+        <v>4.148709535598755</v>
       </c>
       <c r="L5" t="n">
-        <v>4.019107580184937</v>
+        <v>4.215373134613037</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.876617431640625</v>
+        <v>4.117814064025879</v>
       </c>
       <c r="C6" t="n">
-        <v>4.273098707199097</v>
+        <v>4.068913698196411</v>
       </c>
       <c r="D6" t="n">
-        <v>3.918528079986572</v>
+        <v>4.446434020996094</v>
       </c>
       <c r="E6" t="n">
-        <v>4.148470878601074</v>
+        <v>4.498776197433472</v>
       </c>
       <c r="F6" t="n">
-        <v>3.902556657791138</v>
+        <v>3.909310817718506</v>
       </c>
       <c r="G6" t="n">
-        <v>3.886114835739136</v>
+        <v>4.233047962188721</v>
       </c>
       <c r="H6" t="n">
-        <v>3.830248355865479</v>
+        <v>4.434958934783936</v>
       </c>
       <c r="I6" t="n">
-        <v>3.975388526916504</v>
+        <v>4.352521419525146</v>
       </c>
       <c r="J6" t="n">
-        <v>3.921511173248291</v>
+        <v>4.218851327896118</v>
       </c>
       <c r="K6" t="n">
-        <v>4.048207998275757</v>
+        <v>4.181331157684326</v>
       </c>
       <c r="L6" t="n">
-        <v>3.978074264526367</v>
+        <v>4.246195960044861</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>3.964394330978394</v>
+        <v>4.220249891281128</v>
       </c>
       <c r="C7" t="n">
-        <v>4.470112085342407</v>
+        <v>3.904536247253418</v>
       </c>
       <c r="D7" t="n">
-        <v>3.996819257736206</v>
+        <v>3.990827560424805</v>
       </c>
       <c r="E7" t="n">
-        <v>3.774393558502197</v>
+        <v>3.946439743041992</v>
       </c>
       <c r="F7" t="n">
-        <v>3.707053899765015</v>
+        <v>4.149458408355713</v>
       </c>
       <c r="G7" t="n">
-        <v>3.949450254440308</v>
+        <v>4.615246295928955</v>
       </c>
       <c r="H7" t="n">
-        <v>4.008795738220215</v>
+        <v>3.798318386077881</v>
       </c>
       <c r="I7" t="n">
-        <v>3.72200608253479</v>
+        <v>3.953428268432617</v>
       </c>
       <c r="J7" t="n">
-        <v>3.816276788711548</v>
+        <v>3.895577192306519</v>
       </c>
       <c r="K7" t="n">
-        <v>3.869642972946167</v>
+        <v>3.869636535644531</v>
       </c>
       <c r="L7" t="n">
-        <v>3.927894496917725</v>
+        <v>4.034371852874756</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.12897777557373</v>
+        <v>4.6341712474823</v>
       </c>
       <c r="C8" t="n">
-        <v>4.282639026641846</v>
+        <v>4.338484048843384</v>
       </c>
       <c r="D8" t="n">
-        <v>4.185852766036987</v>
+        <v>4.181354284286499</v>
       </c>
       <c r="E8" t="n">
-        <v>3.862654685974121</v>
+        <v>4.204279661178589</v>
       </c>
       <c r="F8" t="n">
-        <v>4.003793954849243</v>
+        <v>4.191303014755249</v>
       </c>
       <c r="G8" t="n">
-        <v>4.011804103851318</v>
+        <v>4.503037452697754</v>
       </c>
       <c r="H8" t="n">
-        <v>3.887606143951416</v>
+        <v>4.033724784851074</v>
       </c>
       <c r="I8" t="n">
-        <v>3.797324419021606</v>
+        <v>4.264635562896729</v>
       </c>
       <c r="J8" t="n">
-        <v>3.712049245834351</v>
+        <v>4.21127462387085</v>
       </c>
       <c r="K8" t="n">
-        <v>4.015763998031616</v>
+        <v>4.535939931869507</v>
       </c>
       <c r="L8" t="n">
-        <v>3.988846611976624</v>
+        <v>4.309820461273193</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.546453475952148</v>
+        <v>3.802316904067993</v>
       </c>
       <c r="C9" t="n">
-        <v>3.565919637680054</v>
+        <v>3.842203140258789</v>
       </c>
       <c r="D9" t="n">
-        <v>3.934497833251953</v>
+        <v>3.618765830993652</v>
       </c>
       <c r="E9" t="n">
-        <v>3.480624198913574</v>
+        <v>4.479087114334106</v>
       </c>
       <c r="F9" t="n">
-        <v>3.630746364593506</v>
+        <v>3.778359889984131</v>
       </c>
       <c r="G9" t="n">
-        <v>3.650695562362671</v>
+        <v>3.852175712585449</v>
       </c>
       <c r="H9" t="n">
-        <v>3.398338794708252</v>
+        <v>3.982869148254395</v>
       </c>
       <c r="I9" t="n">
-        <v>3.440750360488892</v>
+        <v>3.766408681869507</v>
       </c>
       <c r="J9" t="n">
-        <v>4.41378378868103</v>
+        <v>4.310539960861206</v>
       </c>
       <c r="K9" t="n">
-        <v>3.468157529830933</v>
+        <v>3.85816216468811</v>
       </c>
       <c r="L9" t="n">
-        <v>3.652996754646301</v>
+        <v>3.929088854789734</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.58432674407959</v>
+        <v>4.8900465965271</v>
       </c>
       <c r="C10" t="n">
-        <v>4.40477728843689</v>
+        <v>5.022174835205078</v>
       </c>
       <c r="D10" t="n">
-        <v>5.053125381469727</v>
+        <v>5.698975563049316</v>
       </c>
       <c r="E10" t="n">
-        <v>4.957411289215088</v>
+        <v>5.277056694030762</v>
       </c>
       <c r="F10" t="n">
-        <v>4.731469869613647</v>
+        <v>5.237646102905273</v>
       </c>
       <c r="G10" t="n">
-        <v>4.846647500991821</v>
+        <v>5.06009578704834</v>
       </c>
       <c r="H10" t="n">
-        <v>5.207765340805054</v>
+        <v>5.43665623664856</v>
       </c>
       <c r="I10" t="n">
-        <v>5.615687847137451</v>
+        <v>5.552335739135742</v>
       </c>
       <c r="J10" t="n">
-        <v>4.716494798660278</v>
+        <v>5.274088382720947</v>
       </c>
       <c r="K10" t="n">
-        <v>4.763887166976929</v>
+        <v>5.879984855651855</v>
       </c>
       <c r="L10" t="n">
-        <v>4.888159322738647</v>
+        <v>5.332906079292298</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>5.261122703552246</v>
+        <v>5.286499500274658</v>
       </c>
       <c r="C11" t="n">
-        <v>4.609285354614258</v>
+        <v>5.177807569503784</v>
       </c>
       <c r="D11" t="n">
-        <v>4.126981735229492</v>
+        <v>4.383905410766602</v>
       </c>
       <c r="E11" t="n">
-        <v>4.268623352050781</v>
+        <v>4.660112142562866</v>
       </c>
       <c r="F11" t="n">
-        <v>4.310523271560669</v>
+        <v>5.039686918258667</v>
       </c>
       <c r="G11" t="n">
-        <v>4.792809009552002</v>
+        <v>4.848644018173218</v>
       </c>
       <c r="H11" t="n">
-        <v>3.920510292053223</v>
+        <v>4.650136232376099</v>
       </c>
       <c r="I11" t="n">
-        <v>4.008780241012573</v>
+        <v>4.281581401824951</v>
       </c>
       <c r="J11" t="n">
-        <v>4.69305419921875</v>
+        <v>4.879061222076416</v>
       </c>
       <c r="K11" t="n">
-        <v>4.419240713119507</v>
+        <v>4.515024662017822</v>
       </c>
       <c r="L11" t="n">
-        <v>4.44109308719635</v>
+        <v>4.772245907783509</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.982334852218628</v>
+        <v>4.165881395339966</v>
       </c>
       <c r="C12" t="n">
-        <v>4.111015796661377</v>
+        <v>4.149485111236572</v>
       </c>
       <c r="D12" t="n">
-        <v>3.80031681060791</v>
+        <v>4.010785102844238</v>
       </c>
       <c r="E12" t="n">
-        <v>4.071153402328491</v>
+        <v>4.256136178970337</v>
       </c>
       <c r="F12" t="n">
-        <v>3.694085121154785</v>
+        <v>4.07112193107605</v>
       </c>
       <c r="G12" t="n">
-        <v>4.255208730697632</v>
+        <v>4.329480409622192</v>
       </c>
       <c r="H12" t="n">
-        <v>3.974092245101929</v>
+        <v>4.240176677703857</v>
       </c>
       <c r="I12" t="n">
-        <v>4.267913341522217</v>
+        <v>4.232701778411865</v>
       </c>
       <c r="J12" t="n">
-        <v>3.701863050460815</v>
+        <v>4.106034994125366</v>
       </c>
       <c r="K12" t="n">
-        <v>3.913325309753418</v>
+        <v>4.403793334960938</v>
       </c>
       <c r="L12" t="n">
-        <v>3.97713086605072</v>
+        <v>4.196559691429139</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.878817081451416</v>
+        <v>4.867579460144043</v>
       </c>
       <c r="C13" t="n">
-        <v>4.925686120986938</v>
+        <v>5.21967887878418</v>
       </c>
       <c r="D13" t="n">
-        <v>4.598062038421631</v>
+        <v>5.48201847076416</v>
       </c>
       <c r="E13" t="n">
-        <v>4.270396947860718</v>
+        <v>5.412209033966064</v>
       </c>
       <c r="F13" t="n">
-        <v>4.484334468841553</v>
+        <v>5.089559555053711</v>
       </c>
       <c r="G13" t="n">
-        <v>4.820311069488525</v>
+        <v>5.104473352432251</v>
       </c>
       <c r="H13" t="n">
-        <v>4.669344663619995</v>
+        <v>4.598268508911133</v>
       </c>
       <c r="I13" t="n">
-        <v>5.152118682861328</v>
+        <v>5.381773471832275</v>
       </c>
       <c r="J13" t="n">
-        <v>5.59745192527771</v>
+        <v>5.155412197113037</v>
       </c>
       <c r="K13" t="n">
-        <v>5.443525314331055</v>
+        <v>4.447409391403198</v>
       </c>
       <c r="L13" t="n">
-        <v>4.884004831314087</v>
+        <v>5.075838232040406</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.214272260665894</v>
+        <v>4.447411060333252</v>
       </c>
       <c r="C14" t="n">
-        <v>4.300544738769531</v>
+        <v>4.134727716445923</v>
       </c>
       <c r="D14" t="n">
-        <v>4.123005151748657</v>
+        <v>4.380621671676636</v>
       </c>
       <c r="E14" t="n">
-        <v>3.982361078262329</v>
+        <v>4.697288036346436</v>
       </c>
       <c r="F14" t="n">
-        <v>3.91906213760376</v>
+        <v>4.942628860473633</v>
       </c>
       <c r="G14" t="n">
-        <v>4.360408782958984</v>
+        <v>4.400533199310303</v>
       </c>
       <c r="H14" t="n">
-        <v>4.151917934417725</v>
+        <v>5.306698083877563</v>
       </c>
       <c r="I14" t="n">
-        <v>5.348381519317627</v>
+        <v>4.590050935745239</v>
       </c>
       <c r="J14" t="n">
-        <v>3.963391542434692</v>
+        <v>4.501328706741333</v>
       </c>
       <c r="K14" t="n">
-        <v>4.006789207458496</v>
+        <v>4.423710346221924</v>
       </c>
       <c r="L14" t="n">
-        <v>4.237013435363769</v>
+        <v>4.582499861717224</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.189353942871094</v>
+        <v>5.13739275932312</v>
       </c>
       <c r="C15" t="n">
-        <v>4.800781965255737</v>
+        <v>4.690540075302124</v>
       </c>
       <c r="D15" t="n">
-        <v>4.771370410919189</v>
+        <v>4.742405891418457</v>
       </c>
       <c r="E15" t="n">
-        <v>4.32747745513916</v>
+        <v>5.436651468276978</v>
       </c>
       <c r="F15" t="n">
-        <v>4.244709730148315</v>
+        <v>4.840648174285889</v>
       </c>
       <c r="G15" t="n">
-        <v>4.409772396087646</v>
+        <v>4.693535566329956</v>
       </c>
       <c r="H15" t="n">
-        <v>4.291580200195312</v>
+        <v>5.184267997741699</v>
       </c>
       <c r="I15" t="n">
-        <v>5.821167945861816</v>
+        <v>4.611270189285278</v>
       </c>
       <c r="J15" t="n">
-        <v>4.950889825820923</v>
+        <v>4.765847444534302</v>
       </c>
       <c r="K15" t="n">
-        <v>4.45714807510376</v>
+        <v>5.101533889770508</v>
       </c>
       <c r="L15" t="n">
-        <v>4.626425194740295</v>
+        <v>4.920409345626831</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.27209997177124</v>
+        <v>4.397798776626587</v>
       </c>
       <c r="C16" t="n">
-        <v>3.800311326980591</v>
+        <v>4.190316438674927</v>
       </c>
       <c r="D16" t="n">
-        <v>4.065158367156982</v>
+        <v>4.441673040390015</v>
       </c>
       <c r="E16" t="n">
-        <v>3.734970569610596</v>
+        <v>4.311508417129517</v>
       </c>
       <c r="F16" t="n">
-        <v>3.970883131027222</v>
+        <v>4.242166519165039</v>
       </c>
       <c r="G16" t="n">
-        <v>4.137976408004761</v>
+        <v>4.247692584991455</v>
       </c>
       <c r="H16" t="n">
-        <v>4.601269721984863</v>
+        <v>4.179819583892822</v>
       </c>
       <c r="I16" t="n">
-        <v>4.099063158035278</v>
+        <v>4.149439334869385</v>
       </c>
       <c r="J16" t="n">
-        <v>4.073630094528198</v>
+        <v>4.336438655853271</v>
       </c>
       <c r="K16" t="n">
-        <v>3.912532806396484</v>
+        <v>4.137948036193848</v>
       </c>
       <c r="L16" t="n">
-        <v>4.066789555549621</v>
+        <v>4.263480138778687</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.233724355697632</v>
+        <v>4.163871288299561</v>
       </c>
       <c r="C17" t="n">
-        <v>4.045859098434448</v>
+        <v>4.314487218856812</v>
       </c>
       <c r="D17" t="n">
-        <v>5.193552017211914</v>
+        <v>4.99926233291626</v>
       </c>
       <c r="E17" t="n">
-        <v>3.941240549087524</v>
+        <v>4.379838228225708</v>
       </c>
       <c r="F17" t="n">
-        <v>4.413532495498657</v>
+        <v>4.463610172271729</v>
       </c>
       <c r="G17" t="n">
-        <v>4.033495426177979</v>
+        <v>4.802859783172607</v>
       </c>
       <c r="H17" t="n">
-        <v>3.930790901184082</v>
+        <v>4.832677364349365</v>
       </c>
       <c r="I17" t="n">
-        <v>4.599035978317261</v>
+        <v>4.459126234054565</v>
       </c>
       <c r="J17" t="n">
-        <v>4.111796855926514</v>
+        <v>4.440675973892212</v>
       </c>
       <c r="K17" t="n">
-        <v>4.516767501831055</v>
+        <v>4.792773008346558</v>
       </c>
       <c r="L17" t="n">
-        <v>4.301979517936706</v>
+        <v>4.564918160438538</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.166169404983521</v>
+        <v>4.43720555305481</v>
       </c>
       <c r="C18" t="n">
-        <v>4.566638708114624</v>
+        <v>4.726465463638306</v>
       </c>
       <c r="D18" t="n">
-        <v>4.228029727935791</v>
+        <v>4.503993988037109</v>
       </c>
       <c r="E18" t="n">
-        <v>4.428506851196289</v>
+        <v>4.689043045043945</v>
       </c>
       <c r="F18" t="n">
-        <v>3.952728033065796</v>
+        <v>4.339955806732178</v>
       </c>
       <c r="G18" t="n">
-        <v>4.432470083236694</v>
+        <v>4.872573375701904</v>
       </c>
       <c r="H18" t="n">
-        <v>4.075905561447144</v>
+        <v>4.548412561416626</v>
       </c>
       <c r="I18" t="n">
-        <v>4.290339946746826</v>
+        <v>4.851635932922363</v>
       </c>
       <c r="J18" t="n">
-        <v>5.142130374908447</v>
+        <v>5.224667072296143</v>
       </c>
       <c r="K18" t="n">
-        <v>6.389938592910767</v>
+        <v>4.389827489852905</v>
       </c>
       <c r="L18" t="n">
-        <v>4.56728572845459</v>
+        <v>4.658378028869629</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.028522968292236</v>
+        <v>4.637741565704346</v>
       </c>
       <c r="C19" t="n">
-        <v>3.791132211685181</v>
+        <v>4.132941722869873</v>
       </c>
       <c r="D19" t="n">
-        <v>4.148447036743164</v>
+        <v>4.28757119178772</v>
       </c>
       <c r="E19" t="n">
-        <v>4.149714946746826</v>
+        <v>4.58281135559082</v>
       </c>
       <c r="F19" t="n">
-        <v>4.573105812072754</v>
+        <v>4.162404537200928</v>
       </c>
       <c r="G19" t="n">
-        <v>3.989623546600342</v>
+        <v>4.409760713577271</v>
       </c>
       <c r="H19" t="n">
-        <v>4.233990907669067</v>
+        <v>4.62321138381958</v>
       </c>
       <c r="I19" t="n">
-        <v>3.821053743362427</v>
+        <v>4.128027677536011</v>
       </c>
       <c r="J19" t="n">
-        <v>4.004578351974487</v>
+        <v>4.136953830718994</v>
       </c>
       <c r="K19" t="n">
-        <v>3.911343574523926</v>
+        <v>4.262649059295654</v>
       </c>
       <c r="L19" t="n">
-        <v>4.065151309967041</v>
+        <v>4.33640730381012</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.42648458480835</v>
+        <v>5.875601768493652</v>
       </c>
       <c r="C20" t="n">
-        <v>4.343698263168335</v>
+        <v>4.67082953453064</v>
       </c>
       <c r="D20" t="n">
-        <v>4.859404325485229</v>
+        <v>5.062319040298462</v>
       </c>
       <c r="E20" t="n">
-        <v>4.341710090637207</v>
+        <v>5.549057245254517</v>
       </c>
       <c r="F20" t="n">
-        <v>4.898249387741089</v>
+        <v>5.267801523208618</v>
       </c>
       <c r="G20" t="n">
-        <v>4.549179315567017</v>
+        <v>5.036879539489746</v>
       </c>
       <c r="H20" t="n">
-        <v>4.582091808319092</v>
+        <v>5.349557876586914</v>
       </c>
       <c r="I20" t="n">
-        <v>4.886325120925903</v>
+        <v>5.371057033538818</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3033287525177</v>
+        <v>5.499186038970947</v>
       </c>
       <c r="K20" t="n">
-        <v>4.522744655609131</v>
+        <v>5.473736524581909</v>
       </c>
       <c r="L20" t="n">
-        <v>4.571321630477906</v>
+        <v>5.315602612495423</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>3.96569037437439</v>
+        <v>5.366570472717285</v>
       </c>
       <c r="C21" t="n">
-        <v>4.094843149185181</v>
+        <v>4.507748126983643</v>
       </c>
       <c r="D21" t="n">
-        <v>4.494808673858643</v>
+        <v>4.648881435394287</v>
       </c>
       <c r="E21" t="n">
-        <v>4.05544638633728</v>
+        <v>4.111789703369141</v>
       </c>
       <c r="F21" t="n">
-        <v>4.42250394821167</v>
+        <v>4.794525146484375</v>
       </c>
       <c r="G21" t="n">
-        <v>4.109804630279541</v>
+        <v>4.669365406036377</v>
       </c>
       <c r="H21" t="n">
-        <v>4.268397569656372</v>
+        <v>4.741146564483643</v>
       </c>
       <c r="I21" t="n">
-        <v>4.79351282119751</v>
+        <v>4.733184576034546</v>
       </c>
       <c r="J21" t="n">
-        <v>4.227013826370239</v>
+        <v>4.480817556381226</v>
       </c>
       <c r="K21" t="n">
-        <v>4.408231019973755</v>
+        <v>4.152186870574951</v>
       </c>
       <c r="L21" t="n">
-        <v>4.284025239944458</v>
+        <v>4.620621585845948</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.220276355743408</v>
+        <v>4.499780654907227</v>
       </c>
       <c r="C22" t="n">
-        <v>4.31751537322998</v>
+        <v>4.542676210403442</v>
       </c>
       <c r="D22" t="n">
-        <v>5.023240327835083</v>
+        <v>4.850364923477173</v>
       </c>
       <c r="E22" t="n">
-        <v>4.277595281600952</v>
+        <v>4.707284927368164</v>
       </c>
       <c r="F22" t="n">
-        <v>4.020770311355591</v>
+        <v>4.601030349731445</v>
       </c>
       <c r="G22" t="n">
-        <v>4.842656373977661</v>
+        <v>4.69226598739624</v>
       </c>
       <c r="H22" t="n">
-        <v>4.590311050415039</v>
+        <v>4.554658889770508</v>
       </c>
       <c r="I22" t="n">
-        <v>4.335438013076782</v>
+        <v>4.527216672897339</v>
       </c>
       <c r="J22" t="n">
-        <v>4.424715518951416</v>
+        <v>4.672904014587402</v>
       </c>
       <c r="K22" t="n">
-        <v>4.194310665130615</v>
+        <v>4.845877647399902</v>
       </c>
       <c r="L22" t="n">
-        <v>4.424682927131653</v>
+        <v>4.649406027793884</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>3.909543752670288</v>
+        <v>4.978042364120483</v>
       </c>
       <c r="C23" t="n">
-        <v>3.972874641418457</v>
+        <v>4.433451652526855</v>
       </c>
       <c r="D23" t="n">
-        <v>3.932468414306641</v>
+        <v>4.193097591400146</v>
       </c>
       <c r="E23" t="n">
-        <v>4.183353900909424</v>
+        <v>4.258926391601562</v>
       </c>
       <c r="F23" t="n">
-        <v>4.135995388031006</v>
+        <v>4.079885959625244</v>
       </c>
       <c r="G23" t="n">
-        <v>4.036717414855957</v>
+        <v>4.626950740814209</v>
       </c>
       <c r="H23" t="n">
-        <v>4.216264009475708</v>
+        <v>4.332226991653442</v>
       </c>
       <c r="I23" t="n">
-        <v>4.337976694107056</v>
+        <v>4.496800422668457</v>
       </c>
       <c r="J23" t="n">
-        <v>4.223260641098022</v>
+        <v>4.875811576843262</v>
       </c>
       <c r="K23" t="n">
-        <v>4.04571008682251</v>
+        <v>4.229028463363647</v>
       </c>
       <c r="L23" t="n">
-        <v>4.099416494369507</v>
+        <v>4.450422215461731</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.645668029785156</v>
+        <v>4.372628450393677</v>
       </c>
       <c r="C24" t="n">
-        <v>4.632197618484497</v>
+        <v>4.651882886886597</v>
       </c>
       <c r="D24" t="n">
-        <v>4.382861375808716</v>
+        <v>5.445358753204346</v>
       </c>
       <c r="E24" t="n">
-        <v>4.520999193191528</v>
+        <v>4.701238632202148</v>
       </c>
       <c r="F24" t="n">
-        <v>4.396811246871948</v>
+        <v>4.754117727279663</v>
       </c>
       <c r="G24" t="n">
-        <v>4.228251695632935</v>
+        <v>5.169532775878906</v>
       </c>
       <c r="H24" t="n">
-        <v>4.36637020111084</v>
+        <v>4.727909088134766</v>
       </c>
       <c r="I24" t="n">
-        <v>4.182386875152588</v>
+        <v>4.535945177078247</v>
       </c>
       <c r="J24" t="n">
-        <v>4.783833980560303</v>
+        <v>5.140419960021973</v>
       </c>
       <c r="K24" t="n">
-        <v>4.411762237548828</v>
+        <v>4.887058258056641</v>
       </c>
       <c r="L24" t="n">
-        <v>4.455114245414734</v>
+        <v>4.838609170913696</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.397789716720581</v>
+        <v>4.372856855392456</v>
       </c>
       <c r="C25" t="n">
-        <v>4.398401260375977</v>
+        <v>4.385668516159058</v>
       </c>
       <c r="D25" t="n">
-        <v>4.387853384017944</v>
+        <v>4.536682605743408</v>
       </c>
       <c r="E25" t="n">
-        <v>4.038728952407837</v>
+        <v>4.649892807006836</v>
       </c>
       <c r="F25" t="n">
-        <v>4.631219148635864</v>
+        <v>4.611983060836792</v>
       </c>
       <c r="G25" t="n">
-        <v>4.524969577789307</v>
+        <v>4.46589207649231</v>
       </c>
       <c r="H25" t="n">
-        <v>5.317954540252686</v>
+        <v>4.117765426635742</v>
       </c>
       <c r="I25" t="n">
-        <v>4.54545521736145</v>
+        <v>6.840051174163818</v>
       </c>
       <c r="J25" t="n">
-        <v>4.806249141693115</v>
+        <v>4.622775554656982</v>
       </c>
       <c r="K25" t="n">
-        <v>4.36388635635376</v>
+        <v>4.816470861434937</v>
       </c>
       <c r="L25" t="n">
-        <v>4.541250729560852</v>
+        <v>4.742003893852234</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.209279775619507</v>
+        <v>4.591060638427734</v>
       </c>
       <c r="C26" t="n">
-        <v>4.954904317855835</v>
+        <v>4.450425863265991</v>
       </c>
       <c r="D26" t="n">
-        <v>4.351947069168091</v>
+        <v>4.53222918510437</v>
       </c>
       <c r="E26" t="n">
-        <v>3.932154417037964</v>
+        <v>4.486322641372681</v>
       </c>
       <c r="F26" t="n">
-        <v>3.790330410003662</v>
+        <v>4.941145181655884</v>
       </c>
       <c r="G26" t="n">
-        <v>4.420736789703369</v>
+        <v>4.846367120742798</v>
       </c>
       <c r="H26" t="n">
-        <v>4.036703109741211</v>
+        <v>4.421489477157593</v>
       </c>
       <c r="I26" t="n">
-        <v>4.079100608825684</v>
+        <v>4.893767833709717</v>
       </c>
       <c r="J26" t="n">
-        <v>4.076125860214233</v>
+        <v>4.429459095001221</v>
       </c>
       <c r="K26" t="n">
-        <v>4.108058214187622</v>
+        <v>4.411508798599243</v>
       </c>
       <c r="L26" t="n">
-        <v>4.195934057235718</v>
+        <v>4.600377583503723</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>3.825251817703247</v>
+        <v>4.07689356803894</v>
       </c>
       <c r="C27" t="n">
-        <v>3.886628150939941</v>
+        <v>4.214030504226685</v>
       </c>
       <c r="D27" t="n">
-        <v>3.797343015670776</v>
+        <v>4.150185108184814</v>
       </c>
       <c r="E27" t="n">
-        <v>3.835226535797119</v>
+        <v>4.361143350601196</v>
       </c>
       <c r="F27" t="n">
-        <v>4.110037088394165</v>
+        <v>4.175129652023315</v>
       </c>
       <c r="G27" t="n">
-        <v>3.671634197235107</v>
+        <v>4.710278511047363</v>
       </c>
       <c r="H27" t="n">
-        <v>4.332000494003296</v>
+        <v>4.219009399414062</v>
       </c>
       <c r="I27" t="n">
-        <v>3.786844968795776</v>
+        <v>4.320243120193481</v>
       </c>
       <c r="J27" t="n">
-        <v>3.696091413497925</v>
+        <v>4.137741088867188</v>
       </c>
       <c r="K27" t="n">
-        <v>3.804310083389282</v>
+        <v>4.193064451217651</v>
       </c>
       <c r="L27" t="n">
-        <v>3.874536776542663</v>
+        <v>4.25577187538147</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.343961715698242</v>
+        <v>4.346689224243164</v>
       </c>
       <c r="C28" t="n">
-        <v>3.998816728591919</v>
+        <v>4.089353322982788</v>
       </c>
       <c r="D28" t="n">
-        <v>3.988333940505981</v>
+        <v>4.503780126571655</v>
       </c>
       <c r="E28" t="n">
-        <v>3.914530277252197</v>
+        <v>4.100818634033203</v>
       </c>
       <c r="F28" t="n">
-        <v>4.181348562240601</v>
+        <v>4.36762523651123</v>
       </c>
       <c r="G28" t="n">
-        <v>4.043710947036743</v>
+        <v>4.480830192565918</v>
       </c>
       <c r="H28" t="n">
-        <v>4.249691247940063</v>
+        <v>3.99608325958252</v>
       </c>
       <c r="I28" t="n">
-        <v>4.042710065841675</v>
+        <v>4.62048077583313</v>
       </c>
       <c r="J28" t="n">
-        <v>3.783380270004272</v>
+        <v>3.911308288574219</v>
       </c>
       <c r="K28" t="n">
-        <v>3.71504020690918</v>
+        <v>4.186599731445312</v>
       </c>
       <c r="L28" t="n">
-        <v>4.026152396202088</v>
+        <v>4.260356879234314</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.163420438766479</v>
+        <v>4.334763288497925</v>
       </c>
       <c r="C29" t="n">
-        <v>4.205327749252319</v>
+        <v>4.269224405288696</v>
       </c>
       <c r="D29" t="n">
-        <v>4.366384267807007</v>
+        <v>4.291555404663086</v>
       </c>
       <c r="E29" t="n">
-        <v>3.748947143554688</v>
+        <v>5.096504926681519</v>
       </c>
       <c r="F29" t="n">
-        <v>4.010789394378662</v>
+        <v>4.287618637084961</v>
       </c>
       <c r="G29" t="n">
-        <v>3.865644216537476</v>
+        <v>4.562873125076294</v>
       </c>
       <c r="H29" t="n">
-        <v>4.526963710784912</v>
+        <v>4.381833076477051</v>
       </c>
       <c r="I29" t="n">
-        <v>4.119002819061279</v>
+        <v>4.459137201309204</v>
       </c>
       <c r="J29" t="n">
-        <v>4.162403345108032</v>
+        <v>4.88552188873291</v>
       </c>
       <c r="K29" t="n">
-        <v>4.226297378540039</v>
+        <v>5.024204015731812</v>
       </c>
       <c r="L29" t="n">
-        <v>4.13951804637909</v>
+        <v>4.559323596954346</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.492065668106079</v>
+        <v>4.667608022689819</v>
       </c>
       <c r="C30" t="n">
-        <v>4.154913902282715</v>
+        <v>4.70450496673584</v>
       </c>
       <c r="D30" t="n">
-        <v>4.097054719924927</v>
+        <v>4.580330371856689</v>
       </c>
       <c r="E30" t="n">
-        <v>4.232224464416504</v>
+        <v>4.24517035484314</v>
       </c>
       <c r="F30" t="n">
-        <v>3.940958738327026</v>
+        <v>4.181340932846069</v>
       </c>
       <c r="G30" t="n">
-        <v>4.095076322555542</v>
+        <v>4.522968292236328</v>
       </c>
       <c r="H30" t="n">
-        <v>4.552902698516846</v>
+        <v>4.157925605773926</v>
       </c>
       <c r="I30" t="n">
-        <v>4.048704862594604</v>
+        <v>4.471114873886108</v>
       </c>
       <c r="J30" t="n">
-        <v>4.106029510498047</v>
+        <v>4.135955095291138</v>
       </c>
       <c r="K30" t="n">
-        <v>4.091076612472534</v>
+        <v>4.223242998123169</v>
       </c>
       <c r="L30" t="n">
-        <v>4.181100749969483</v>
+        <v>4.389016151428223</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.982300996780396</v>
+        <v>5.453082084655762</v>
       </c>
       <c r="C31" t="n">
-        <v>5.168369770050049</v>
+        <v>4.808740139007568</v>
       </c>
       <c r="D31" t="n">
-        <v>5.017775535583496</v>
+        <v>4.685564041137695</v>
       </c>
       <c r="E31" t="n">
-        <v>4.879593133926392</v>
+        <v>5.477537155151367</v>
       </c>
       <c r="F31" t="n">
-        <v>5.261125564575195</v>
+        <v>4.857622385025024</v>
       </c>
       <c r="G31" t="n">
-        <v>4.860636234283447</v>
+        <v>4.957860231399536</v>
       </c>
       <c r="H31" t="n">
-        <v>5.149914026260376</v>
+        <v>4.984290361404419</v>
       </c>
       <c r="I31" t="n">
-        <v>4.863604068756104</v>
+        <v>5.601715564727783</v>
       </c>
       <c r="J31" t="n">
-        <v>5.955367088317871</v>
+        <v>4.634163618087769</v>
       </c>
       <c r="K31" t="n">
-        <v>4.884119987487793</v>
+        <v>5.253122806549072</v>
       </c>
       <c r="L31" t="n">
-        <v>5.102280640602112</v>
+        <v>5.0713698387146</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.891043424606323</v>
+        <v>5.23566722869873</v>
       </c>
       <c r="C32" t="n">
-        <v>4.639227390289307</v>
+        <v>4.546895265579224</v>
       </c>
       <c r="D32" t="n">
-        <v>4.462161302566528</v>
+        <v>4.480076789855957</v>
       </c>
       <c r="E32" t="n">
-        <v>4.687622785568237</v>
+        <v>4.622225761413574</v>
       </c>
       <c r="F32" t="n">
-        <v>4.617250204086304</v>
+        <v>4.783821105957031</v>
       </c>
       <c r="G32" t="n">
-        <v>4.908055543899536</v>
+        <v>4.680577278137207</v>
       </c>
       <c r="H32" t="n">
-        <v>4.61428165435791</v>
+        <v>4.811775684356689</v>
       </c>
       <c r="I32" t="n">
-        <v>4.828716039657593</v>
+        <v>5.37781023979187</v>
       </c>
       <c r="J32" t="n">
-        <v>4.66513729095459</v>
+        <v>4.537436008453369</v>
       </c>
       <c r="K32" t="n">
-        <v>4.759901285171509</v>
+        <v>4.52892804145813</v>
       </c>
       <c r="L32" t="n">
-        <v>4.707339692115784</v>
+        <v>4.760521340370178</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.835715055465698</v>
+        <v>4.377611637115479</v>
       </c>
       <c r="C33" t="n">
-        <v>4.812770843505859</v>
+        <v>4.989998817443848</v>
       </c>
       <c r="D33" t="n">
-        <v>4.744945049285889</v>
+        <v>4.59355092048645</v>
       </c>
       <c r="E33" t="n">
-        <v>4.714501857757568</v>
+        <v>4.340704917907715</v>
       </c>
       <c r="F33" t="n">
-        <v>4.589828729629517</v>
+        <v>4.575580596923828</v>
       </c>
       <c r="G33" t="n">
-        <v>4.584333896636963</v>
+        <v>4.530206441879272</v>
       </c>
       <c r="H33" t="n">
-        <v>4.625274896621704</v>
+        <v>4.806490898132324</v>
       </c>
       <c r="I33" t="n">
-        <v>4.539460420608521</v>
+        <v>4.603021144866943</v>
       </c>
       <c r="J33" t="n">
-        <v>4.322522163391113</v>
+        <v>4.607503890991211</v>
       </c>
       <c r="K33" t="n">
-        <v>4.606305837631226</v>
+        <v>5.004000186920166</v>
       </c>
       <c r="L33" t="n">
-        <v>4.637565875053406</v>
+        <v>4.642866945266723</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.908566951751709</v>
+        <v>4.240973472595215</v>
       </c>
       <c r="C34" t="n">
-        <v>3.842216730117798</v>
+        <v>3.867913961410522</v>
       </c>
       <c r="D34" t="n">
-        <v>4.177368640899658</v>
+        <v>4.11430549621582</v>
       </c>
       <c r="E34" t="n">
-        <v>3.896619319915771</v>
+        <v>3.833032608032227</v>
       </c>
       <c r="F34" t="n">
-        <v>4.2691969871521</v>
+        <v>3.809077739715576</v>
       </c>
       <c r="G34" t="n">
-        <v>4.084124803543091</v>
+        <v>4.767078876495361</v>
       </c>
       <c r="H34" t="n">
-        <v>3.948472023010254</v>
+        <v>4.066926240921021</v>
       </c>
       <c r="I34" t="n">
-        <v>4.046324729919434</v>
+        <v>3.821050405502319</v>
       </c>
       <c r="J34" t="n">
-        <v>3.803321123123169</v>
+        <v>3.866435766220093</v>
       </c>
       <c r="K34" t="n">
-        <v>4.027761697769165</v>
+        <v>4.399558305740356</v>
       </c>
       <c r="L34" t="n">
-        <v>4.000397300720214</v>
+        <v>4.078635287284851</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>3.991897583007812</v>
+        <v>4.000607252120972</v>
       </c>
       <c r="C35" t="n">
-        <v>3.916565895080566</v>
+        <v>3.64549994468689</v>
       </c>
       <c r="D35" t="n">
-        <v>5.087563991546631</v>
+        <v>4.846292495727539</v>
       </c>
       <c r="E35" t="n">
-        <v>3.921521186828613</v>
+        <v>4.343216180801392</v>
       </c>
       <c r="F35" t="n">
-        <v>3.653742790222168</v>
+        <v>3.75422215461731</v>
       </c>
       <c r="G35" t="n">
-        <v>3.840226173400879</v>
+        <v>4.084463357925415</v>
       </c>
       <c r="H35" t="n">
-        <v>3.973915100097656</v>
+        <v>4.104032039642334</v>
       </c>
       <c r="I35" t="n">
-        <v>3.967922687530518</v>
+        <v>3.959437370300293</v>
       </c>
       <c r="J35" t="n">
-        <v>3.95245623588562</v>
+        <v>3.787350177764893</v>
       </c>
       <c r="K35" t="n">
-        <v>4.570453882217407</v>
+        <v>3.580864906311035</v>
       </c>
       <c r="L35" t="n">
-        <v>4.087626552581787</v>
+        <v>4.010598587989807</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>4.478606700897217</v>
+        <v>4.272106409072876</v>
       </c>
       <c r="C36" t="n">
-        <v>4.345973014831543</v>
+        <v>4.864602327346802</v>
       </c>
       <c r="D36" t="n">
-        <v>4.028742551803589</v>
+        <v>4.30750846862793</v>
       </c>
       <c r="E36" t="n">
-        <v>4.51203179359436</v>
+        <v>4.293607473373413</v>
       </c>
       <c r="F36" t="n">
-        <v>4.901045560836792</v>
+        <v>4.85664963722229</v>
       </c>
       <c r="G36" t="n">
-        <v>4.126009464263916</v>
+        <v>4.752897024154663</v>
       </c>
       <c r="H36" t="n">
-        <v>4.388832092285156</v>
+        <v>5.275547027587891</v>
       </c>
       <c r="I36" t="n">
-        <v>4.782329559326172</v>
+        <v>4.334975242614746</v>
       </c>
       <c r="J36" t="n">
-        <v>4.876130104064941</v>
+        <v>4.687043190002441</v>
       </c>
       <c r="K36" t="n">
-        <v>4.115022420883179</v>
+        <v>4.203300714492798</v>
       </c>
       <c r="L36" t="n">
-        <v>4.455472326278686</v>
+        <v>4.584823751449585</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.336412191390991</v>
+        <v>5.86954140663147</v>
       </c>
       <c r="C37" t="n">
-        <v>5.21672534942627</v>
+        <v>5.294505596160889</v>
       </c>
       <c r="D37" t="n">
-        <v>6.233149766921997</v>
+        <v>4.806763648986816</v>
       </c>
       <c r="E37" t="n">
-        <v>6.654055595397949</v>
+        <v>5.329950332641602</v>
       </c>
       <c r="F37" t="n">
-        <v>5.686033010482788</v>
+        <v>5.223186492919922</v>
       </c>
       <c r="G37" t="n">
-        <v>4.834741353988647</v>
+        <v>5.496973037719727</v>
       </c>
       <c r="H37" t="n">
-        <v>5.472583055496216</v>
+        <v>5.115452527999878</v>
       </c>
       <c r="I37" t="n">
-        <v>5.555399656295776</v>
+        <v>4.767347574234009</v>
       </c>
       <c r="J37" t="n">
-        <v>5.126466035842896</v>
+        <v>4.88904070854187</v>
       </c>
       <c r="K37" t="n">
-        <v>5.196804285049438</v>
+        <v>4.702509641647339</v>
       </c>
       <c r="L37" t="n">
-        <v>5.531237030029297</v>
+        <v>5.149527096748352</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>3.751968622207642</v>
+        <v>4.148899793624878</v>
       </c>
       <c r="C38" t="n">
-        <v>3.954938173294067</v>
+        <v>4.241207838058472</v>
       </c>
       <c r="D38" t="n">
-        <v>4.304533720016479</v>
+        <v>4.157428503036499</v>
       </c>
       <c r="E38" t="n">
-        <v>3.800302982330322</v>
+        <v>4.087088823318481</v>
       </c>
       <c r="F38" t="n">
-        <v>4.004307985305786</v>
+        <v>4.110044956207275</v>
       </c>
       <c r="G38" t="n">
-        <v>3.798324346542358</v>
+        <v>3.816266775131226</v>
       </c>
       <c r="H38" t="n">
-        <v>3.802313089370728</v>
+        <v>4.457636117935181</v>
       </c>
       <c r="I38" t="n">
-        <v>3.595858812332153</v>
+        <v>4.160420417785645</v>
       </c>
       <c r="J38" t="n">
-        <v>3.707053184509277</v>
+        <v>3.820283889770508</v>
       </c>
       <c r="K38" t="n">
-        <v>3.803330898284912</v>
+        <v>4.066626071929932</v>
       </c>
       <c r="L38" t="n">
-        <v>3.852293181419372</v>
+        <v>4.106590318679809</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>3.751463174819946</v>
+        <v>4.538913726806641</v>
       </c>
       <c r="C39" t="n">
-        <v>4.18482518196106</v>
+        <v>4.170376539230347</v>
       </c>
       <c r="D39" t="n">
-        <v>4.405782222747803</v>
+        <v>4.672107458114624</v>
       </c>
       <c r="E39" t="n">
-        <v>4.004809141159058</v>
+        <v>4.379841327667236</v>
       </c>
       <c r="F39" t="n">
-        <v>3.680164575576782</v>
+        <v>4.209268808364868</v>
       </c>
       <c r="G39" t="n">
-        <v>4.143563985824585</v>
+        <v>4.343447208404541</v>
       </c>
       <c r="H39" t="n">
-        <v>3.762418270111084</v>
+        <v>4.103190422058105</v>
       </c>
       <c r="I39" t="n">
-        <v>3.939462900161743</v>
+        <v>4.003574132919312</v>
       </c>
       <c r="J39" t="n">
-        <v>3.804310083389282</v>
+        <v>4.009573221206665</v>
       </c>
       <c r="K39" t="n">
-        <v>3.936492919921875</v>
+        <v>4.034493684768677</v>
       </c>
       <c r="L39" t="n">
-        <v>3.961329245567322</v>
+        <v>4.246478652954101</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>5.333534479141235</v>
+        <v>4.855333805084229</v>
       </c>
       <c r="C40" t="n">
-        <v>4.489311695098877</v>
+        <v>5.430858373641968</v>
       </c>
       <c r="D40" t="n">
-        <v>4.602029800415039</v>
+        <v>5.005970001220703</v>
       </c>
       <c r="E40" t="n">
-        <v>4.394582748413086</v>
+        <v>5.55354642868042</v>
       </c>
       <c r="F40" t="n">
-        <v>4.579082012176514</v>
+        <v>4.619951009750366</v>
       </c>
       <c r="G40" t="n">
-        <v>4.753135681152344</v>
+        <v>4.869319677352905</v>
       </c>
       <c r="H40" t="n">
-        <v>4.651428461074829</v>
+        <v>5.181095838546753</v>
       </c>
       <c r="I40" t="n">
-        <v>4.251939296722412</v>
+        <v>4.6935875415802</v>
       </c>
       <c r="J40" t="n">
-        <v>4.262425422668457</v>
+        <v>5.254611968994141</v>
       </c>
       <c r="K40" t="n">
-        <v>4.819468021392822</v>
+        <v>5.274057388305664</v>
       </c>
       <c r="L40" t="n">
-        <v>4.613693761825561</v>
+        <v>5.073833203315735</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>3.724794626235962</v>
+        <v>4.410744667053223</v>
       </c>
       <c r="C41" t="n">
-        <v>4.092873811721802</v>
+        <v>4.248153448104858</v>
       </c>
       <c r="D41" t="n">
-        <v>4.134748697280884</v>
+        <v>4.009768486022949</v>
       </c>
       <c r="E41" t="n">
-        <v>4.089871883392334</v>
+        <v>4.21225905418396</v>
       </c>
       <c r="F41" t="n">
-        <v>4.055445909500122</v>
+        <v>4.800770044326782</v>
       </c>
       <c r="G41" t="n">
-        <v>3.81507682800293</v>
+        <v>4.702517509460449</v>
       </c>
       <c r="H41" t="n">
-        <v>3.974640846252441</v>
+        <v>4.788818359375</v>
       </c>
       <c r="I41" t="n">
-        <v>4.404594421386719</v>
+        <v>4.281568288803101</v>
       </c>
       <c r="J41" t="n">
-        <v>4.135688066482544</v>
+        <v>4.466604232788086</v>
       </c>
       <c r="K41" t="n">
-        <v>3.910349607467651</v>
+        <v>4.358906269073486</v>
       </c>
       <c r="L41" t="n">
-        <v>4.033808469772339</v>
+        <v>4.428011035919189</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.35017991065979</v>
+        <v>4.749383211135864</v>
       </c>
       <c r="C42" t="n">
-        <v>4.735204696655273</v>
+        <v>4.617264032363892</v>
       </c>
       <c r="D42" t="n">
-        <v>4.444423675537109</v>
+        <v>5.199734687805176</v>
       </c>
       <c r="E42" t="n">
-        <v>4.451953411102295</v>
+        <v>5.24414324760437</v>
       </c>
       <c r="F42" t="n">
-        <v>4.377116918563843</v>
+        <v>4.685032844543457</v>
       </c>
       <c r="G42" t="n">
-        <v>4.267388105392456</v>
+        <v>5.038652658462524</v>
       </c>
       <c r="H42" t="n">
-        <v>4.394594430923462</v>
+        <v>4.7713303565979</v>
       </c>
       <c r="I42" t="n">
-        <v>4.472411632537842</v>
+        <v>4.965360879898071</v>
       </c>
       <c r="J42" t="n">
-        <v>4.26240873336792</v>
+        <v>5.080032348632812</v>
       </c>
       <c r="K42" t="n">
-        <v>4.271379470825195</v>
+        <v>4.86609411239624</v>
       </c>
       <c r="L42" t="n">
-        <v>4.402706098556519</v>
+        <v>4.92170283794403</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.899741888046265</v>
+        <v>4.892030954360962</v>
       </c>
       <c r="C43" t="n">
-        <v>4.634933233261108</v>
+        <v>5.22967791557312</v>
       </c>
       <c r="D43" t="n">
-        <v>4.192086935043335</v>
+        <v>4.916948080062866</v>
       </c>
       <c r="E43" t="n">
-        <v>4.236970663070679</v>
+        <v>5.010233402252197</v>
       </c>
       <c r="F43" t="n">
-        <v>5.058838129043579</v>
+        <v>5.144386768341064</v>
       </c>
       <c r="G43" t="n">
-        <v>5.040399074554443</v>
+        <v>4.891535520553589</v>
       </c>
       <c r="H43" t="n">
-        <v>4.346191167831421</v>
+        <v>4.760883092880249</v>
       </c>
       <c r="I43" t="n">
-        <v>4.805501222610474</v>
+        <v>4.871594190597534</v>
       </c>
       <c r="J43" t="n">
-        <v>4.719206809997559</v>
+        <v>4.753910541534424</v>
       </c>
       <c r="K43" t="n">
-        <v>4.450421571731567</v>
+        <v>5.307477474212646</v>
       </c>
       <c r="L43" t="n">
-        <v>4.638429069519043</v>
+        <v>4.977867794036865</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.177646398544312</v>
+        <v>4.720250606536865</v>
       </c>
       <c r="C44" t="n">
-        <v>5.139648199081421</v>
+        <v>4.67432713508606</v>
       </c>
       <c r="D44" t="n">
-        <v>4.317275047302246</v>
+        <v>4.469361066818237</v>
       </c>
       <c r="E44" t="n">
-        <v>4.713249921798706</v>
+        <v>4.547169923782349</v>
       </c>
       <c r="F44" t="n">
-        <v>4.145706653594971</v>
+        <v>4.586564779281616</v>
       </c>
       <c r="G44" t="n">
-        <v>4.799501657485962</v>
+        <v>4.338733673095703</v>
       </c>
       <c r="H44" t="n">
-        <v>4.083904981613159</v>
+        <v>4.983548641204834</v>
       </c>
       <c r="I44" t="n">
-        <v>4.442449808120728</v>
+        <v>4.196064233779907</v>
       </c>
       <c r="J44" t="n">
-        <v>4.640935659408569</v>
+        <v>4.40754246711731</v>
       </c>
       <c r="K44" t="n">
-        <v>4.220551490783691</v>
+        <v>4.108806133270264</v>
       </c>
       <c r="L44" t="n">
-        <v>4.468086981773377</v>
+        <v>4.503236865997314</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>3.72181248664856</v>
+        <v>4.320257663726807</v>
       </c>
       <c r="C45" t="n">
-        <v>4.204061508178711</v>
+        <v>4.178134441375732</v>
       </c>
       <c r="D45" t="n">
-        <v>3.869928598403931</v>
+        <v>4.000591993331909</v>
       </c>
       <c r="E45" t="n">
-        <v>3.964682340621948</v>
+        <v>4.427492618560791</v>
       </c>
       <c r="F45" t="n">
-        <v>4.105888605117798</v>
+        <v>4.516727447509766</v>
       </c>
       <c r="G45" t="n">
-        <v>4.200085401535034</v>
+        <v>3.700860738754272</v>
       </c>
       <c r="H45" t="n">
-        <v>3.829049110412598</v>
+        <v>4.298312187194824</v>
       </c>
       <c r="I45" t="n">
-        <v>3.886385202407837</v>
+        <v>4.0549476146698</v>
       </c>
       <c r="J45" t="n">
-        <v>3.789631843566895</v>
+        <v>3.97714638710022</v>
       </c>
       <c r="K45" t="n">
-        <v>4.043977022171021</v>
+        <v>4.173141956329346</v>
       </c>
       <c r="L45" t="n">
-        <v>3.961550211906433</v>
+        <v>4.164761304855347</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.2130446434021</v>
+        <v>4.408535718917847</v>
       </c>
       <c r="C46" t="n">
-        <v>4.11877179145813</v>
+        <v>4.481161117553711</v>
       </c>
       <c r="D46" t="n">
-        <v>4.238970279693604</v>
+        <v>4.501041173934937</v>
       </c>
       <c r="E46" t="n">
-        <v>4.100854396820068</v>
+        <v>5.0232093334198</v>
       </c>
       <c r="F46" t="n">
-        <v>4.599026203155518</v>
+        <v>4.541914224624634</v>
       </c>
       <c r="G46" t="n">
-        <v>4.163180828094482</v>
+        <v>4.393814563751221</v>
       </c>
       <c r="H46" t="n">
-        <v>4.370137929916382</v>
+        <v>4.450167894363403</v>
       </c>
       <c r="I46" t="n">
-        <v>3.905339479446411</v>
+        <v>4.565849542617798</v>
       </c>
       <c r="J46" t="n">
-        <v>4.847900629043579</v>
+        <v>4.812757253646851</v>
       </c>
       <c r="K46" t="n">
-        <v>4.261903524398804</v>
+        <v>4.582062482833862</v>
       </c>
       <c r="L46" t="n">
-        <v>4.281912970542908</v>
+        <v>4.576051330566406</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.033500671386719</v>
+        <v>3.869419574737549</v>
       </c>
       <c r="C47" t="n">
-        <v>3.8724365234375</v>
+        <v>4.247963905334473</v>
       </c>
       <c r="D47" t="n">
-        <v>3.627559423446655</v>
+        <v>3.862447023391724</v>
       </c>
       <c r="E47" t="n">
-        <v>3.731797218322754</v>
+        <v>4.26591420173645</v>
       </c>
       <c r="F47" t="n">
-        <v>3.921814441680908</v>
+        <v>4.926691055297852</v>
       </c>
       <c r="G47" t="n">
-        <v>4.002082824707031</v>
+        <v>3.844491004943848</v>
       </c>
       <c r="H47" t="n">
-        <v>3.693928241729736</v>
+        <v>5.111176490783691</v>
       </c>
       <c r="I47" t="n">
-        <v>3.91522479057312</v>
+        <v>3.891389608383179</v>
       </c>
       <c r="J47" t="n">
-        <v>3.637256860733032</v>
+        <v>4.296801805496216</v>
       </c>
       <c r="K47" t="n">
-        <v>3.566204309463501</v>
+        <v>3.948719024658203</v>
       </c>
       <c r="L47" t="n">
-        <v>3.800180530548096</v>
+        <v>4.226501369476319</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>5.026427745819092</v>
+        <v>4.673343658447266</v>
       </c>
       <c r="C48" t="n">
-        <v>4.231977224349976</v>
+        <v>4.876312017440796</v>
       </c>
       <c r="D48" t="n">
-        <v>4.375106811523438</v>
+        <v>4.904741764068604</v>
       </c>
       <c r="E48" t="n">
-        <v>4.371641635894775</v>
+        <v>4.979062080383301</v>
       </c>
       <c r="F48" t="n">
-        <v>4.543687582015991</v>
+        <v>5.131165504455566</v>
       </c>
       <c r="G48" t="n">
-        <v>4.727215528488159</v>
+        <v>4.914693117141724</v>
       </c>
       <c r="H48" t="n">
-        <v>4.394570827484131</v>
+        <v>5.247881650924683</v>
       </c>
       <c r="I48" t="n">
-        <v>4.436949253082275</v>
+        <v>4.75812029838562</v>
       </c>
       <c r="J48" t="n">
-        <v>4.367135047912598</v>
+        <v>4.653392791748047</v>
       </c>
       <c r="K48" t="n">
-        <v>4.497815132141113</v>
+        <v>4.594540357589722</v>
       </c>
       <c r="L48" t="n">
-        <v>4.497252678871154</v>
+        <v>4.873325324058532</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.433463573455811</v>
+        <v>4.546698331832886</v>
       </c>
       <c r="C49" t="n">
-        <v>4.07689094543457</v>
+        <v>4.788528203964233</v>
       </c>
       <c r="D49" t="n">
-        <v>4.420514822006226</v>
+        <v>4.808497667312622</v>
       </c>
       <c r="E49" t="n">
-        <v>5.036916494369507</v>
+        <v>4.522716045379639</v>
       </c>
       <c r="F49" t="n">
-        <v>4.503782033920288</v>
+        <v>4.774066925048828</v>
       </c>
       <c r="G49" t="n">
-        <v>4.626958847045898</v>
+        <v>4.418999195098877</v>
       </c>
       <c r="H49" t="n">
-        <v>4.793544292449951</v>
+        <v>4.901235580444336</v>
       </c>
       <c r="I49" t="n">
-        <v>4.209065675735474</v>
+        <v>4.280360698699951</v>
       </c>
       <c r="J49" t="n">
-        <v>4.526710748672485</v>
+        <v>4.753624439239502</v>
       </c>
       <c r="K49" t="n">
-        <v>3.986618995666504</v>
+        <v>5.126178026199341</v>
       </c>
       <c r="L49" t="n">
-        <v>4.461446642875671</v>
+        <v>4.692090511322021</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.939253091812134</v>
+        <v>3.742744922637939</v>
       </c>
       <c r="C50" t="n">
-        <v>3.533304691314697</v>
+        <v>4.112793684005737</v>
       </c>
       <c r="D50" t="n">
-        <v>4.192122220993042</v>
+        <v>3.770201206207275</v>
       </c>
       <c r="E50" t="n">
-        <v>3.939752578735352</v>
+        <v>3.90731954574585</v>
       </c>
       <c r="F50" t="n">
-        <v>3.52034330368042</v>
+        <v>4.434447288513184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.868924140930176</v>
+        <v>4.050960779190063</v>
       </c>
       <c r="H50" t="n">
-        <v>3.725804328918457</v>
+        <v>3.963202476501465</v>
       </c>
       <c r="I50" t="n">
-        <v>3.843492031097412</v>
+        <v>4.295308828353882</v>
       </c>
       <c r="J50" t="n">
-        <v>3.692894220352173</v>
+        <v>4.395548582077026</v>
       </c>
       <c r="K50" t="n">
-        <v>3.844000101089478</v>
+        <v>3.896397352218628</v>
       </c>
       <c r="L50" t="n">
-        <v>3.809989070892334</v>
+        <v>4.056892466545105</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.56711483001709</v>
+        <v>4.465367317199707</v>
       </c>
       <c r="C51" t="n">
-        <v>4.238102436065674</v>
+        <v>4.942136287689209</v>
       </c>
       <c r="D51" t="n">
-        <v>5.034180402755737</v>
+        <v>4.676850557327271</v>
       </c>
       <c r="E51" t="n">
-        <v>4.133950233459473</v>
+        <v>4.746666431427002</v>
       </c>
       <c r="F51" t="n">
-        <v>4.208275079727173</v>
+        <v>4.553905963897705</v>
       </c>
       <c r="G51" t="n">
-        <v>4.344958305358887</v>
+        <v>5.083564281463623</v>
       </c>
       <c r="H51" t="n">
-        <v>4.572871685028076</v>
+        <v>5.005261182785034</v>
       </c>
       <c r="I51" t="n">
-        <v>5.143928050994873</v>
+        <v>4.035703897476196</v>
       </c>
       <c r="J51" t="n">
-        <v>4.038768291473389</v>
+        <v>4.61922812461853</v>
       </c>
       <c r="K51" t="n">
-        <v>4.15394401550293</v>
+        <v>4.83816385269165</v>
       </c>
       <c r="L51" t="n">
-        <v>4.44360933303833</v>
+        <v>4.696684789657593</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.311182956695557</v>
+        <v>4.558959765434265</v>
       </c>
       <c r="C52" t="n">
-        <v>4.329443488121033</v>
+        <v>4.497794771194458</v>
       </c>
       <c r="D52" t="n">
-        <v>4.409661545753479</v>
+        <v>4.535385890007019</v>
       </c>
       <c r="E52" t="n">
-        <v>4.256387577056885</v>
+        <v>4.587504467964172</v>
       </c>
       <c r="F52" t="n">
-        <v>4.274372158050537</v>
+        <v>4.526113872528076</v>
       </c>
       <c r="G52" t="n">
-        <v>4.293546867370606</v>
+        <v>4.569308924674988</v>
       </c>
       <c r="H52" t="n">
-        <v>4.303363628387451</v>
+        <v>4.586042604446411</v>
       </c>
       <c r="I52" t="n">
-        <v>4.381410903930664</v>
+        <v>4.517872257232666</v>
       </c>
       <c r="J52" t="n">
-        <v>4.313058118820191</v>
+        <v>4.498661565780639</v>
       </c>
       <c r="K52" t="n">
-        <v>4.277446737289429</v>
+        <v>4.498557238578797</v>
       </c>
       <c r="L52" t="n">
-        <v>4.314987398147583</v>
+        <v>4.537620135784149</v>
       </c>
     </row>
   </sheetData>
